--- a/excel/distribuidora-sol-del-valle-s-a-c_efectivos.xlsx
+++ b/excel/distribuidora-sol-del-valle-s-a-c_efectivos.xlsx
@@ -563,17 +563,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C001512631</t>
+          <t>C001628609</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C001512631 - LOPEZ CHAVEZ YAQUELIN PATRICIA</t>
+          <t>C001628609 - RODRIGUEZ ROBLES ALBERTO ROGER</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
@@ -586,18 +586,18 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>No tiene celulae</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -628,12 +628,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C001513040</t>
+          <t>C001333647</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C001513040 - ACOSTA FERNANDEZ MARCELINA ESTHER</t>
+          <t>C001333647 - GALLARDO BARRETO JORGE LUIS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -662,25 +662,13 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No desea usar apps</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -705,12 +693,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C001331144</t>
+          <t>C001512631</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C001331144 - INFANTES CHACON YOLANDA MARINA</t>
+          <t>C001512631 - LOPEZ CHAVEZ YAQUELIN PATRICIA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -739,25 +727,13 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene celulae</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -782,17 +758,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C001628609</t>
+          <t>C001513040</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C001628609 - RODRIGUEZ ROBLES ALBERTO ROGER</t>
+          <t>C001513040 - ACOSTA FERNANDEZ MARCELINA ESTHER</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
@@ -805,12 +781,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -820,9 +796,21 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -924,17 +912,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C001639514</t>
+          <t>C001331144</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C001639514 - SANCHEZ PEREZ MARITZA ISELA</t>
+          <t>C001331144 - INFANTES CHACON YOLANDA MARINA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
@@ -947,12 +935,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -962,9 +950,21 @@
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -989,17 +989,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C001669043</t>
+          <t>C001639514</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C001669043 - ORBEGOSO MUÑOZ EMELDA ELIZABETH</t>
+          <t>C001639514 - SANCHEZ PEREZ MARITZA ISELA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1027,21 +1027,9 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1066,17 +1054,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C001735407</t>
+          <t>C001331147</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C001735407 - GUTIERREZ ROSALES PEDRO MARCOS</t>
+          <t>C001331147 - PEREZ ESQUIVEL ANITA RAQUEL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
@@ -1089,12 +1077,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1104,9 +1092,21 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1208,17 +1208,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C001331147</t>
+          <t>C001331347</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C001331147 - PEREZ ESQUIVEL ANITA RAQUEL</t>
+          <t>C001331347 - FARROÑAN BALDERA BALTAZARA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1246,21 +1246,9 @@
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1285,12 +1273,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C001333647</t>
+          <t>C001483227</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C001333647 - GALLARDO BARRETO JORGE LUIS</t>
+          <t>C001483227 - VILLANUEVA HILARIO CYNTHIA YESENIA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1319,13 +1307,25 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>No desea usar apps</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1350,17 +1350,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C001331347</t>
+          <t>C001669043</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C001331347 - FARROÑAN BALDERA BALTAZARA</t>
+          <t>C001669043 - ORBEGOSO MUÑOZ EMELDA ELIZABETH</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
@@ -1373,12 +1373,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1388,9 +1388,21 @@
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1415,17 +1427,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C001483227</t>
+          <t>C001735407</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C001483227 - VILLANUEVA HILARIO CYNTHIA YESENIA</t>
+          <t>C001735407 - GUTIERREZ ROSALES PEDRO MARCOS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
@@ -1438,12 +1450,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1453,21 +1465,9 @@
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C001661625</t>
+          <t>C001732698</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C001661625 - RODRIGUEZ HORNA ELENA MARI</t>
+          <t>C001732698 - TICLIAHUANCA REYNA MARILYN FLORENCIA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1526,17 +1526,25 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Usa iphone</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1561,17 +1569,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>C001683933</t>
+          <t>C001331142</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C001683933 - ARMAS DIAZ FAUSTA MERCEDES</t>
+          <t>C001331142 - FERREL LOPEZ DE LAZARO TOMASA TERESA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
@@ -1584,12 +1592,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1599,9 +1607,21 @@
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1626,12 +1646,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C001331142</t>
+          <t>C001674351</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C001331142 - FERREL LOPEZ DE LAZARO TOMASA TERESA</t>
+          <t>C001674351 - YSIDRO SOCORRO ANELIDA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1688,7 +1708,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1703,12 +1723,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C001674351</t>
+          <t>C001661625</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C001674351 - YSIDRO SOCORRO ANELIDA</t>
+          <t>C001661625 - RODRIGUEZ HORNA ELENA MARI</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1737,25 +1757,17 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+          <t>Usa iphone</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1780,17 +1792,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C001732698</t>
+          <t>C001683933</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C001732698 - TICLIAHUANCA REYNA MARILYN FLORENCIA</t>
+          <t>C001683933 - ARMAS DIAZ FAUSTA MERCEDES</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
@@ -1803,12 +1815,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1818,21 +1830,9 @@
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1857,17 +1857,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C004176767</t>
+          <t>C004048840</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C004176767 - MANRIQUE VILLARREAL MARILU</t>
+          <t>C004048840 - CORTIJO NEYRA LUCERO DEL CIELO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1895,9 +1895,21 @@
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1922,12 +1934,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>C001717735</t>
+          <t>C004184682</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C001717735 - CASTAÑEDA CASTILLO JULIO CESAR</t>
+          <t>C004184682 - SUAREZ RODRIGUEZ LEONEL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1950,7 +1962,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1987,17 +1999,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>C001760417</t>
+          <t>C001717735</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C001760417 - BOCANEGRA HILARIO JHOORDYN AQUILES</t>
+          <t>C001717735 - CASTAÑEDA CASTILLO JULIO CESAR</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
@@ -2010,12 +2022,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -2025,21 +2037,9 @@
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>C004184682</t>
+          <t>C001760417</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C004184682 - SUAREZ RODRIGUEZ LEONEL</t>
+          <t>C001760417 - BOCANEGRA HILARIO JHOORDYN AQUILES</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -2102,9 +2102,21 @@
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2129,17 +2141,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>C004048840</t>
+          <t>C004176767</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C004048840 - CORTIJO NEYRA LUCERO DEL CIELO</t>
+          <t>C004176767 - MANRIQUE VILLARREAL MARILU</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
@@ -2152,12 +2164,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -2167,21 +2179,9 @@
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>C004185437</t>
+          <t>C004197221</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>C004185437 - ZAVALETA BAYLON PAOLA NOEMI</t>
+          <t>C004197221 - VARGAS REYES ARCADIO MODESTO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>C004197150</t>
+          <t>C004185437</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C004197150 - PONCE DOMINGUEZ MARIA PILAR</t>
+          <t>C004185437 - ZAVALETA BAYLON PAOLA NOEMI</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>C004197221</t>
+          <t>C004197150</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C004197221 - VARGAS REYES ARCADIO MODESTO</t>
+          <t>C004197150 - PONCE DOMINGUEZ MARIA PILAR</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2437,17 +2437,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>C001563276</t>
+          <t>C001751731</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C001563276 - MENDEZ MENDEZ DEROMILDA</t>
+          <t>C001751731 - RODRIGUEZ SARE JANETH ALICIA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -2475,21 +2475,9 @@
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2499,7 +2487,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2514,12 +2502,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>C004190467</t>
+          <t>C001740965</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C004190467 - GARCIA FAJARDO JAMPOOL JUNIOR</t>
+          <t>C001740965 - LAZARO NICASIO MARIBEL KARINA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2551,7 +2539,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
           <t>Muy dispuesto</t>
@@ -2564,7 +2556,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2660,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>C001751731</t>
+          <t>C004190467</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C001751731 - RODRIGUEZ SARE JANETH ALICIA</t>
+          <t>C004190467 - GARCIA FAJARDO JAMPOOL JUNIOR</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
@@ -2691,12 +2683,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2706,9 +2698,21 @@
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2718,7 +2722,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2733,17 +2737,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>C001740965</t>
+          <t>C001703145</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>C001740965 - LAZARO NICASIO MARIBEL KARINA</t>
+          <t>C001703145 - GONZALES ZAVALETA YORLIN DARLIN</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
@@ -2756,12 +2760,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2770,26 +2774,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2799,7 +2787,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2814,12 +2802,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>C001679465</t>
+          <t>C004168484</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>C001679465 - LAUREANO QUEZADA EVELYN NOEMI</t>
+          <t>C004168484 - ROJAS POLO LISBETH SANTA ANA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2842,7 +2830,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2879,17 +2867,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>C001703145</t>
+          <t>C004059726</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C001703145 - GONZALES ZAVALETA YORLIN DARLIN</t>
+          <t>C004059726 - GERONIMO PEREZ MARINO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
@@ -2902,12 +2890,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2917,9 +2905,21 @@
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>C001678739</t>
+          <t>C001576999</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C001678739 - AVILA PELAEZ ISAI ALDAHIR</t>
+          <t>C001576999 - TORRES LIZARRAGA GIANMARCO ANDRE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2982,9 +2982,21 @@
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3009,12 +3021,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>C004059726</t>
+          <t>C001711464</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C004059726 - GERONIMO PEREZ MARINO</t>
+          <t>C001711464 - DIONICIO HERNANDEZ MIRTA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3151,17 +3163,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>C004168484</t>
+          <t>C001563276</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C004168484 - ROJAS POLO LISBETH SANTA ANA</t>
+          <t>C001563276 - MENDEZ MENDEZ DEROMILDA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
@@ -3174,12 +3186,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -3189,9 +3201,21 @@
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3423,17 +3447,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>C001629991</t>
+          <t>C001678739</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C001629991 - AVILA RODRIGUEZ LADY ROSSELLI</t>
+          <t>C001678739 - AVILA PELAEZ ISAI ALDAHIR</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
@@ -3446,12 +3470,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -3461,21 +3485,9 @@
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Iniciar sesión</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3500,12 +3512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>C001576999</t>
+          <t>C001629991</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C001576999 - TORRES LIZARRAGA GIANMARCO ANDRE</t>
+          <t>C001629991 - AVILA RODRIGUEZ LADY ROSSELLI</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3545,12 +3557,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3651,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3654,17 +3666,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>C001711464</t>
+          <t>C001679465</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C001711464 - DIONICIO HERNANDEZ MIRTA</t>
+          <t>C001679465 - LAUREANO QUEZADA EVELYN NOEMI</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
@@ -3677,12 +3689,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -3692,21 +3704,9 @@
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4015,17 +4015,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>C001332822</t>
+          <t>C001638419</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C001332822 - PINILLOS MARCELO KAREN TATIANA</t>
+          <t>C001638419 - CORPORACION TAYKA G &amp; R S.A.C.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H50" s="2" t="n">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -4053,21 +4053,9 @@
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4092,17 +4080,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>C001638419</t>
+          <t>C001334859</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C001638419 - CORPORACION TAYKA G &amp; R S.A.C.</t>
+          <t>C001334859 - RODRIGUEZ VALDIVIESO LILIAN GLADYS</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
@@ -4115,12 +4103,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -4130,9 +4118,21 @@
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Más productos disponibles</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>C001334859</t>
+          <t>C001332822</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C001334859 - RODRIGUEZ VALDIVIESO LILIAN GLADYS</t>
+          <t>C001332822 - PINILLOS MARCELO KAREN TATIANA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -4234,17 +4234,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>C001336950</t>
+          <t>C001687871</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C001336950 - CRUZADO REYES DIGNA JANET</t>
+          <t>C001687871 - ROMERO PEREZ JESSICA MEDALY</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -4272,9 +4272,21 @@
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4284,7 +4296,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4299,12 +4311,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>C001712645</t>
+          <t>C001731317</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C001712645 - GUTIERREZ ROJAS ELVIN</t>
+          <t>C001731317 - SANCHEZ MOZO MILI YOVANA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4361,7 +4373,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4376,17 +4388,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>C001731317</t>
+          <t>C001336950</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C001731317 - SANCHEZ MOZO MILI YOVANA</t>
+          <t>C001336950 - CRUZADO REYES DIGNA JANET</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H55" s="2" t="n">
@@ -4399,12 +4411,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -4414,21 +4426,9 @@
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4453,17 +4453,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>C001711882</t>
+          <t>C001712645</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>C001711882 - GUEVARA CRUZ SANTOS BERNABITA</t>
+          <t>C001712645 - GUTIERREZ ROJAS ELVIN</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H56" s="2" t="n">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -4491,9 +4491,21 @@
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4518,17 +4530,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>C001687871</t>
+          <t>C001711882</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>C001687871 - ROMERO PEREZ JESSICA MEDALY</t>
+          <t>C001711882 - GUEVARA CRUZ SANTOS BERNABITA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H57" s="2" t="n">
@@ -4541,12 +4553,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -4556,21 +4568,9 @@
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4660,17 +4660,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>C001401674</t>
+          <t>C001741503</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C001401674 - DIAZ CALDERON CARMEN ROCIO</t>
+          <t>C001741503 - FERREL DIESTRA ALEJANDRINA TEONILA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H59" s="2" t="n">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -4698,9 +4698,21 @@
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Iniciar sesión</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4879,12 +4891,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>C004210270</t>
+          <t>C001721553</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C004210270 - VENEGAS VALVERDE VIOLETA IRIS</t>
+          <t>C001721553 - LAZARO VEGA VIRGINIA MAGDALENA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4944,12 +4956,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>C001721553</t>
+          <t>C001401674</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>C001721553 - LAZARO VEGA VIRGINIA MAGDALENA</t>
+          <t>C001401674 - DIAZ CALDERON CARMEN ROCIO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4972,7 +4984,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -5009,12 +5021,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>C001732663</t>
+          <t>C004169281</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>C001732663 - ARTEAGA ACEVEDO MARIA PAULINA</t>
+          <t>C004169281 - SALVADOR PEREIRA LOURDES MARIA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5037,7 +5049,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -5074,17 +5086,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>C001741503</t>
+          <t>C001732663</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C001741503 - FERREL DIESTRA ALEJANDRINA TEONILA</t>
+          <t>C001732663 - ARTEAGA ACEVEDO MARIA PAULINA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H65" s="2" t="n">
@@ -5097,12 +5109,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -5112,21 +5124,9 @@
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Iniciar sesión</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5151,17 +5151,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>C004169281</t>
+          <t>C001513253</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C004169281 - SALVADOR PEREIRA LOURDES MARIA</t>
+          <t>C001513253 - RODRIGUEZ VALDIVIESO YULI DEYSI</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H66" s="2" t="n">
@@ -5174,12 +5174,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -5189,9 +5189,21 @@
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5216,12 +5228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>C001513253</t>
+          <t>C001734971</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C001513253 - RODRIGUEZ VALDIVIESO YULI DEYSI</t>
+          <t>C001734971 - ALVARADO PRADO PEDRO NILTON</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5293,12 +5305,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>C001734971</t>
+          <t>C004170162</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>C001734971 - ALVARADO PRADO PEDRO NILTON</t>
+          <t>C004170162 - RODRIGUEZ RUIZ ADRIANA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5343,7 +5355,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
     </row>
@@ -5370,17 +5382,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>C004170162</t>
+          <t>C004210270</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>C004170162 - RODRIGUEZ RUIZ ADRIANA</t>
+          <t>C004210270 - VENEGAS VALVERDE VIOLETA IRIS</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H69" s="2" t="n">
@@ -5393,12 +5405,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -5408,21 +5420,9 @@
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>C001564265</t>
+          <t>C004173672</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>C001564265 - ROJAS PONCE MAXIMO ESTUARDO</t>
+          <t>C004173672 - ROJAS JUAREZ ANA MARIA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5719,17 +5719,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>C001731770</t>
+          <t>C001564265</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C001731770 - BENITEZ RODRIGUEZ SEGUNDA FLORESTINA</t>
+          <t>C001564265 - ROJAS PONCE MAXIMO ESTUARDO</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H74" s="2" t="n">
@@ -5742,12 +5742,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -5757,21 +5757,9 @@
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5796,12 +5784,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>C001682053</t>
+          <t>C001731770</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C001682053 - CONTRERAS MARQUINA IDAÑA MARDELID</t>
+          <t>C001731770 - BENITEZ RODRIGUEZ SEGUNDA FLORESTINA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5873,17 +5861,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>C004192363</t>
+          <t>C001682053</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C004192363 - VASQUEZ AGUIRRE VICTOR EDUARDO</t>
+          <t>C001682053 - CONTRERAS MARQUINA IDAÑA MARDELID</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H76" s="2" t="n">
@@ -5896,12 +5884,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -5911,9 +5899,21 @@
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>C001739568</t>
+          <t>C004192363</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C001739568 - REYES NAMAY ANTERO AMARANTE</t>
+          <t>C004192363 - VASQUEZ AGUIRRE VICTOR EDUARDO</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>C001713673</t>
+          <t>C001739568</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>C001713673 - GUTIERREZ REYES LUPE AZUCENA</t>
+          <t>C001739568 - REYES NAMAY ANTERO AMARANTE</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>C001737797</t>
+          <t>C001713673</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>C001737797 - RODRIGUEZ AGUSTIN LELIS ARMIDA</t>
+          <t>C001713673 - GUTIERREZ REYES LUPE AZUCENA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>C001712660</t>
+          <t>C001755782</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>C001712660 - CHAVEZ SANCHEZ MILAGROS MARIANELLA</t>
+          <t>C001755782 - TORRES MATTOS ANA ROSA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6244,7 +6244,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>No tiene su celular a la mano</t>
+          <t>No usa apps</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -6275,17 +6275,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>C004173672</t>
+          <t>C001737180</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>C004173672 - ROJAS JUAREZ ANA MARIA</t>
+          <t>C001737180 - CASTILLO RAMIREZ EYLEEN JULICSA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H82" s="2" t="n">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -6313,9 +6313,21 @@
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6340,12 +6352,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>C001755782</t>
+          <t>C001732181</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>C001755782 - TORRES MATTOS ANA ROSA</t>
+          <t>C001732181 - MANTILLA MINCHOLA SARA ESMENIA</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6374,7 +6386,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>No usa apps</t>
+          <t>No usa celular</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -6405,12 +6417,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>C001720753</t>
+          <t>C001733600</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>C001720753 - CASTRO DE VENTURA JUANA</t>
+          <t>C001733600 - REYES CABRERA MELBER AGAPITO</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6439,13 +6451,29 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>No usa celular</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6455,7 +6483,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6470,12 +6498,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>C001750147</t>
+          <t>C001720753</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>C001750147 - JARA GUEVARA KARINE YUDIT</t>
+          <t>C001720753 - CASTRO DE VENTURA JUANA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6504,25 +6532,13 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No usa celular</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6547,17 +6563,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>C001563594</t>
+          <t>C001737797</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>C001563594 - GERONIMO POLO MARLENI DE JESUS</t>
+          <t>C001737797 - RODRIGUEZ AGUSTIN LELIS ARMIDA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H86" s="2" t="n">
@@ -6570,25 +6586,21 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>No usa apps</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
@@ -6616,12 +6628,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>C001667496</t>
+          <t>C001712660</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>C001667496 - RODRIGUEZ AGUILAR FLORA</t>
+          <t>C001712660 - CHAVEZ SANCHEZ MILAGROS MARIANELLA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6650,25 +6662,13 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene su celular a la mano</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>C001669759</t>
+          <t>C001667496</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>C001669759 - CONTRERAS GUTIERREZ ERIKA YESENIA</t>
+          <t>C001667496 - RODRIGUEZ AGUILAR FLORA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6727,13 +6727,25 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Va a pedir su baja, cambio de codigo</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6758,12 +6770,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>C001737180</t>
+          <t>C001669759</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>C001737180 - CASTILLO RAMIREZ EYLEEN JULICSA</t>
+          <t>C001669759 - CONTRERAS GUTIERREZ ERIKA YESENIA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6792,25 +6804,13 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Va a pedir su baja, cambio de codigo</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>C001732181</t>
+          <t>C001750147</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>C001732181 - MANTILLA MINCHOLA SARA ESMENIA</t>
+          <t>C001750147 - JARA GUEVARA KARINE YUDIT</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6869,13 +6869,25 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>No usa celular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6900,12 +6912,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>C001733600</t>
+          <t>C001563594</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>C001733600 - REYES CABRERA MELBER AGAPITO</t>
+          <t>C001563594 - GERONIMO POLO MARLENI DE JESUS</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6934,29 +6946,17 @@
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No usa apps</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>C001371461</t>
+          <t>C001125965</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>C001371461 - BAZAN MOYA LESLIE JULIANA</t>
+          <t>C001125965 - PAISIG ALVA ANA MARIA</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7947,12 +7947,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>C001125965</t>
+          <t>C001371461</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>C001125965 - PAISIG ALVA ANA MARIA</t>
+          <t>C001371461 - BAZAN MOYA LESLIE JULIANA</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -8024,12 +8024,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>C001169862</t>
+          <t>C001324436</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>C001169862 - OSORIO RODRIGUEZ SANTOS MARGARITA</t>
+          <t>C001324436 - PLASENCIA DE CARRERA NIMIA HERMELINDA</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8058,7 +8058,7 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Apps, no se puede registrar</t>
+          <t>No usa apps</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -8089,12 +8089,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>C001324436</t>
+          <t>C001169862</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>C001324436 - PLASENCIA DE CARRERA NIMIA HERMELINDA</t>
+          <t>C001169862 - OSORIO RODRIGUEZ SANTOS MARGARITA</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8123,7 +8123,7 @@
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>No usa apps</t>
+          <t>Apps, no se puede registrar</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
@@ -8154,17 +8154,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>C001178241</t>
+          <t>C001329386</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>C001178241 - VARGAS AVERANGA JUAN CARLOS</t>
+          <t>C001329386 - QUISPE CONDORI VALENTINA</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H109" s="2" t="n">
@@ -8177,18 +8177,18 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>No usa celular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -8219,17 +8219,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>C001400576</t>
+          <t>C001513618</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>C001400576 - JOAQUIN VARAS ROSA VIRGINIA</t>
+          <t>C001513618 - MERCEDES LEDESMA VICTOR ADOLFO</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H110" s="2" t="n">
@@ -8242,12 +8242,12 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -8257,9 +8257,21 @@
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8284,17 +8296,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>C001329386</t>
+          <t>C001178241</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>C001329386 - QUISPE CONDORI VALENTINA</t>
+          <t>C001178241 - VARGAS AVERANGA JUAN CARLOS</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H111" s="2" t="n">
@@ -8307,18 +8319,18 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No usa celular</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -8349,17 +8361,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>C001513618</t>
+          <t>C001400576</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>C001513618 - MERCEDES LEDESMA VICTOR ADOLFO</t>
+          <t>C001400576 - JOAQUIN VARAS ROSA VIRGINIA</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H112" s="2" t="n">
@@ -8372,12 +8384,12 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -8387,21 +8399,9 @@
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>C001130068</t>
+          <t>C001324430</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>C001130068 - CALDERON RODRIGUEZ WILDER YLARIO</t>
+          <t>C001324430 - MORILLAS CABALLERO SANTOS CATALINA</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9105,7 +9105,7 @@
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>No usa apps</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -9136,12 +9136,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>C001324430</t>
+          <t>C001117422</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>C001324430 - MORILLAS CABALLERO SANTOS CATALINA</t>
+          <t>C001117422 - LIZARRAGA GUTIERREZ ANTERO DANIEL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9174,9 +9174,21 @@
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9201,12 +9213,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>C001117422</t>
+          <t>C001130068</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>C001117422 - LIZARRAGA GUTIERREZ ANTERO DANIEL</t>
+          <t>C001130068 - CALDERON RODRIGUEZ WILDER YLARIO</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9235,25 +9247,13 @@
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No usa apps</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P124" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q124" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>C001706255</t>
+          <t>C001115972</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>C001706255 - CRUZ GONZALES HELGA EVELYN</t>
+          <t>C001115972 - BENITES MAURICIO ROSA INES</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9355,12 +9355,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>C001125639</t>
+          <t>C001706255</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>C001125639 - QUIROZ MARIN JUAN EDGARDO</t>
+          <t>C001706255 - CRUZ GONZALES HELGA EVELYN</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -9432,12 +9432,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>C001115972</t>
+          <t>C001125639</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>C001115972 - BENITES MAURICIO ROSA INES</t>
+          <t>C001125639 - QUIROZ MARIN JUAN EDGARDO</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
     </row>
@@ -9509,12 +9509,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>C001179290</t>
+          <t>C001554836</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>C001179290 - CHIZA GUEVARA FLOR ANGELICA</t>
+          <t>C001554836 - MALCA CERCADO SEGUNDO RICARDO</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9586,12 +9586,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>C001125879</t>
+          <t>C001179290</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>C001125879 - GONZALES CHUQUIMANGO ANITA NIEVES</t>
+          <t>C001179290 - CHIZA GUEVARA FLOR ANGELICA</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -9663,12 +9663,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>C001554836</t>
+          <t>C001125879</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>C001554836 - MALCA CERCADO SEGUNDO RICARDO</t>
+          <t>C001125879 - GONZALES CHUQUIMANGO ANITA NIEVES</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>C001179289</t>
+          <t>C004173978</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>C001179289 - ARMAS DE TOCTO MARIA CONVERCION</t>
+          <t>C004173978 - ROMERO BUENO MARIA PILAR</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>C001739792</t>
+          <t>C004175865</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>C001739792 - ALFARO MUÑOZ MARITZA ESTHER</t>
+          <t>C004175865 - ALEJO RUIZ ESTEFANY FELIPA</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
@@ -10089,17 +10089,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>C004169208</t>
+          <t>C001179289</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>C004169208 - GARCIA LEON MARIA MAGDALENA</t>
+          <t>C001179289 - ARMAS DE TOCTO MARIA CONVERCION</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H136" s="2" t="n">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -10127,9 +10127,21 @@
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr"/>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -10154,12 +10166,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>C004199283</t>
+          <t>C004169208</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>C004199283 - VIGO QUISPE DE CAMONES MARILIAN SUXA</t>
+          <t>C004169208 - GARCIA LEON MARIA MAGDALENA</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10182,7 +10194,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
@@ -10219,12 +10231,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>C004177086</t>
+          <t>C001739792</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>C004177086 - SERIN TICLIO GLADIZ</t>
+          <t>C001739792 - ALFARO MUÑOZ MARITZA ESTHER</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10284,17 +10296,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>C004173978</t>
+          <t>C004199283</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>C004173978 - ROMERO BUENO MARIA PILAR</t>
+          <t>C004199283 - VIGO QUISPE DE CAMONES MARILIAN SUXA</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H139" s="2" t="n">
@@ -10307,12 +10319,12 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
@@ -10322,21 +10334,9 @@
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P139" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q139" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -10361,12 +10361,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>C004175865</t>
+          <t>C004177086</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>C004175865 - ALEJO RUIZ ESTEFANY FELIPA</t>
+          <t>C004177086 - SERIN TICLIO GLADIZ</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
@@ -10491,12 +10491,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>C004214055</t>
+          <t>C001763033</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>C004214055 - VILLAR CUEVA EMPERATRIZ</t>
+          <t>C001763033 - QUILICHE ALCALDE ROSA MAGALI</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10556,12 +10556,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>C001763033</t>
+          <t>C004214055</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>C001763033 - QUILICHE ALCALDE ROSA MAGALI</t>
+          <t>C004214055 - VILLAR CUEVA EMPERATRIZ</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>C004214056</t>
+          <t>C004236868</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>C004214056 - AMAYA CAMACHO CARLOS ANTONIO</t>
+          <t>C004236868 - MIÑANO PORTILLA GLORIA</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10655,25 +10655,13 @@
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No desea usar apps, no quiere visitas</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P144" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q144" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10775,12 +10763,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>C004236868</t>
+          <t>C004214056</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>C004236868 - MIÑANO PORTILLA GLORIA</t>
+          <t>C004214056 - AMAYA CAMACHO CARLOS ANTONIO</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10809,13 +10797,25 @@
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>No desea usar apps, no quiere visitas</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="inlineStr"/>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -11295,12 +11295,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>C001735336</t>
+          <t>C001125416</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>C001735336 - CALDERON VILLANUEVA DORALIZ RAQUEL</t>
+          <t>C001125416 - MEDRANO OBANDO JESSICA VANESSA</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>C001125416</t>
+          <t>C001735336</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>C001125416 - MEDRANO OBANDO JESSICA VANESSA</t>
+          <t>C001735336 - CALDERON VILLANUEVA DORALIZ RAQUEL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11624,12 +11624,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>C001127634</t>
+          <t>C001128962</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>C001127634 - VIDAL GARCIA TERESA</t>
+          <t>C001128962 - PAREDES HUAMAN SANTOS PETRONILA</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11701,12 +11701,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>C001128962</t>
+          <t>C001127634</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>C001128962 - PAREDES HUAMAN SANTOS PETRONILA</t>
+          <t>C001127634 - VIDAL GARCIA TERESA</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>C004166670</t>
+          <t>C001578039</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>C004166670 - RODRIGUEZ RODRIGUEZ GABBY ROSSI</t>
+          <t>C001578039 - AGUILAR URRUTIA ROSA KELLY</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12151,12 +12151,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>C001578039</t>
+          <t>C004169210</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>C001578039 - AGUILAR URRUTIA ROSA KELLY</t>
+          <t>C004169210 - LOZADA GONZALES ANGIE PAOLA</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12185,25 +12185,17 @@
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P166" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q166" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+          <t>Celular con bateria baja, para la siguiente visita si desea instalacion</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -12228,12 +12220,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>C004169210</t>
+          <t>C004166670</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>C004169210 - LOZADA GONZALES ANGIE PAOLA</t>
+          <t>C004166670 - RODRIGUEZ RODRIGUEZ GABBY ROSSI</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12262,17 +12254,25 @@
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Celular con bateria baja, para la siguiente visita si desea instalacion</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O167" t="inlineStr"/>
-      <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>C001118560</t>
+          <t>C001567587</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>C001118560 - GIL LEDESMA ROXANA ELIZABETH</t>
+          <t>C001567587 - RUIZ MIÑANO ROSA FLOR</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12331,13 +12331,25 @@
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Trabaja solo credito, no le interesa el apps</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="inlineStr"/>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -12362,17 +12374,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>C001567587</t>
+          <t>C001667630</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>C001567587 - RUIZ MIÑANO ROSA FLOR</t>
+          <t>C001667630 - RODRIGUEZ BALDERA LILIANA YOVANA</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H169" s="2" t="n">
@@ -12385,12 +12397,12 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L169" t="inlineStr"/>
@@ -12400,21 +12412,9 @@
         </is>
       </c>
       <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P169" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -12439,17 +12439,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>C001667630</t>
+          <t>C001118560</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>C001667630 - RODRIGUEZ BALDERA LILIANA YOVANA</t>
+          <t>C001118560 - GIL LEDESMA ROXANA ELIZABETH</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H170" s="2" t="n">
@@ -12462,18 +12462,18 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Trabaja solo credito, no le interesa el apps</t>
         </is>
       </c>
       <c r="N170" t="inlineStr"/>
@@ -12646,12 +12646,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>C001488137</t>
+          <t>C001390118</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>C001488137 - RIOS LEON MIGUEL ANGEL</t>
+          <t>C001390118 - OSORIO POLO ORLANDO JAIME</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L173" t="inlineStr"/>
@@ -12711,17 +12711,17 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>C001518592</t>
+          <t>C001417686</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>C001518592 - ORUNA SAAVEDRA JESUS MANUELA</t>
+          <t>C001417686 - ROJAS ROJALES JUAN AURELIO</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H174" s="2" t="n">
@@ -12734,18 +12734,18 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>No desea usar apps, prefiere su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -12776,12 +12776,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>C001485387</t>
+          <t>C001401994</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>C001485387 - VALDERRAMA ARANDA CHELA SUSANA</t>
+          <t>C001401994 - PAREDES VDA. DE LEON MARIA ALICIA</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L175" t="inlineStr"/>
@@ -12841,12 +12841,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>C001390118</t>
+          <t>C001485387</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>C001390118 - OSORIO POLO ORLANDO JAIME</t>
+          <t>C001485387 - VALDERRAMA ARANDA CHELA SUSANA</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -12869,7 +12869,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L176" t="inlineStr"/>
@@ -12906,17 +12906,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>C001417686</t>
+          <t>C001518592</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>C001417686 - ROJAS ROJALES JUAN AURELIO</t>
+          <t>C001518592 - ORUNA SAAVEDRA JESUS MANUELA</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H177" s="2" t="n">
@@ -12929,18 +12929,18 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No desea usar apps, prefiere su vendedor</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -12971,12 +12971,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>C001401994</t>
+          <t>C001488137</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>C001401994 - PAREDES VDA. DE LEON MARIA ALICIA</t>
+          <t>C001488137 - RIOS LEON MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L178" t="inlineStr"/>
@@ -13401,12 +13401,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>C001736497</t>
+          <t>C004050163</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>C001736497 - VILLENA BECERRA SHUSEY ESTEFANY</t>
+          <t>C004050163 - GARCIA CASTRO ROSMERY ELIZABETH</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -13478,12 +13478,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>C004050163</t>
+          <t>C004241687</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>C004050163 - GARCIA CASTRO ROSMERY ELIZABETH</t>
+          <t>C004241687 - MIGUEL BARRIOS ROSMERY</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -13620,12 +13620,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>C004241687</t>
+          <t>C001736497</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>C004241687 - MIGUEL BARRIOS ROSMERY</t>
+          <t>C001736497 - VILLENA BECERRA SHUSEY ESTEFANY</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14253,12 +14253,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>C004167851</t>
+          <t>C001625528</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>C004167851 - VARAS HERNANDEZ HIMELINA ARANCEL</t>
+          <t>C001625528 - VELASQUEZ IGLESIAS JESSENIA FLOR</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -14287,25 +14287,13 @@
       <c r="L196" t="inlineStr"/>
       <c r="M196" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No desea usar app</t>
         </is>
       </c>
       <c r="N196" t="inlineStr"/>
-      <c r="O196" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P196" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q196" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -14330,12 +14318,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>C001739071</t>
+          <t>C001736078</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>C001739071 - VEREAU ROSARIO SANTOS AIDEE</t>
+          <t>C001736078 - LUJAN ARMAS DINNA</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14364,25 +14352,13 @@
       <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No usa celular</t>
         </is>
       </c>
       <c r="N197" t="inlineStr"/>
-      <c r="O197" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P197" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q197" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -14407,17 +14383,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>C001737406</t>
+          <t>C001733224</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>C001737406 - SEGURA BRICEÑO ALEJANDRINA THALIA</t>
+          <t>C001733224 - BENITES LAZARO MARIA ESTHER</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H198" s="2" t="n">
@@ -14430,12 +14406,12 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L198" t="inlineStr"/>
@@ -14445,9 +14421,21 @@
         </is>
       </c>
       <c r="N198" t="inlineStr"/>
-      <c r="O198" t="inlineStr"/>
-      <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="inlineStr"/>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -14472,17 +14460,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>C001733224</t>
+          <t>C001732066</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>C001733224 - BENITES LAZARO MARIA ESTHER</t>
+          <t>C001732066 - IPARRAGUIRRE DAVILA LORGIO JOVINO</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H199" s="2" t="n">
@@ -14495,12 +14483,12 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L199" t="inlineStr"/>
@@ -14510,21 +14498,9 @@
         </is>
       </c>
       <c r="N199" t="inlineStr"/>
-      <c r="O199" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P199" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q199" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -14549,12 +14525,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>C001625528</t>
+          <t>C001759977</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>C001625528 - VELASQUEZ IGLESIAS JESSENIA FLOR</t>
+          <t>C001759977 - ARENAS VARGAS NAOMI STEPHANY</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -14583,13 +14559,25 @@
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr">
         <is>
-          <t>No desea usar app</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr"/>
-      <c r="P200" t="inlineStr"/>
-      <c r="Q200" t="inlineStr"/>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -14614,12 +14602,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>C001736078</t>
+          <t>C004167851</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>C001736078 - LUJAN ARMAS DINNA</t>
+          <t>C004167851 - VARAS HERNANDEZ HIMELINA ARANCEL</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -14648,13 +14636,25 @@
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr">
         <is>
-          <t>No usa celular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N201" t="inlineStr"/>
-      <c r="O201" t="inlineStr"/>
-      <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="inlineStr"/>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -14679,17 +14679,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>C001732066</t>
+          <t>C001739071</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>C001732066 - IPARRAGUIRRE DAVILA LORGIO JOVINO</t>
+          <t>C001739071 - VEREAU ROSARIO SANTOS AIDEE</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H202" s="2" t="n">
@@ -14702,12 +14702,12 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L202" t="inlineStr"/>
@@ -14717,9 +14717,21 @@
         </is>
       </c>
       <c r="N202" t="inlineStr"/>
-      <c r="O202" t="inlineStr"/>
-      <c r="P202" t="inlineStr"/>
-      <c r="Q202" t="inlineStr"/>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -14744,17 +14756,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>C001759977</t>
+          <t>C001737406</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>C001759977 - ARENAS VARGAS NAOMI STEPHANY</t>
+          <t>C001737406 - SEGURA BRICEÑO ALEJANDRINA THALIA</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H203" s="2" t="n">
@@ -14767,12 +14779,12 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L203" t="inlineStr"/>
@@ -14782,21 +14794,9 @@
         </is>
       </c>
       <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P203" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q203" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -14963,12 +14963,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>C001736049</t>
+          <t>C001727483</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>C001736049 - IPARRAGUIRRE HUACCHA ANITA</t>
+          <t>C001727483 - OTINIANO FLORES DE CARBAJAL JULIA ROSA</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L206" t="inlineStr"/>
@@ -15093,17 +15093,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>C001727483</t>
+          <t>C001737285</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>C001727483 - OTINIANO FLORES DE CARBAJAL JULIA ROSA</t>
+          <t>C001737285 - GUTIERREZ AVILA ZULY JANETH</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H208" s="2" t="n">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L208" t="inlineStr"/>
@@ -15131,9 +15131,21 @@
         </is>
       </c>
       <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr"/>
-      <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="inlineStr"/>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -15158,12 +15170,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>C001737285</t>
+          <t>C001663917</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>C001737285 - GUTIERREZ AVILA ZULY JANETH</t>
+          <t>C001663917 - GARCIA SALAZAR MARIA JANET</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -15192,25 +15204,13 @@
       <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No usa apps</t>
         </is>
       </c>
       <c r="N209" t="inlineStr"/>
-      <c r="O209" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P209" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q209" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -15235,12 +15235,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>C001663917</t>
+          <t>C001708611</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>C001663917 - GARCIA SALAZAR MARIA JANET</t>
+          <t>C001708611 - MINCHOLA ALVARADO PAMELA YUDITH</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -15269,7 +15269,7 @@
       <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr">
         <is>
-          <t>No usa apps</t>
+          <t>Celular con clave</t>
         </is>
       </c>
       <c r="N210" t="inlineStr"/>
@@ -15300,17 +15300,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>C001708611</t>
+          <t>C001127373</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>C001708611 - MINCHOLA ALVARADO PAMELA YUDITH</t>
+          <t>C001127373 - GALLARDO ORBEGOZO YANET JAQUELINE</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H211" s="2" t="n">
@@ -15323,18 +15323,18 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Celular con clave</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N211" t="inlineStr"/>
@@ -15365,12 +15365,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>C001127373</t>
+          <t>C001736049</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>C001127373 - GALLARDO ORBEGOZO YANET JAQUELINE</t>
+          <t>C001736049 - IPARRAGUIRRE HUACCHA ANITA</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15430,12 +15430,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>C001761601</t>
+          <t>C001357277</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>C001761601 - GARCIA ROJAS YAHAIRA XIOMARA</t>
+          <t>C001357277 - ARTEAGA CRESPIN JUANITA</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L213" t="inlineStr"/>
@@ -15495,17 +15495,17 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>C001400565</t>
+          <t>C001674440</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>C001400565 - QUISPE LOZANO SANTOS</t>
+          <t>C001674440 - FLORES PAICO JOSE SANTOS</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H214" s="2" t="n">
@@ -15518,12 +15518,12 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L214" t="inlineStr"/>
@@ -15533,21 +15533,9 @@
         </is>
       </c>
       <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P214" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q214" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -15572,17 +15560,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>C001357277</t>
+          <t>C001400565</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>C001357277 - ARTEAGA CRESPIN JUANITA</t>
+          <t>C001400565 - QUISPE LOZANO SANTOS</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H215" s="2" t="n">
@@ -15595,12 +15583,12 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L215" t="inlineStr"/>
@@ -15610,9 +15598,21 @@
         </is>
       </c>
       <c r="N215" t="inlineStr"/>
-      <c r="O215" t="inlineStr"/>
-      <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="inlineStr"/>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -15637,17 +15637,17 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>C001674440</t>
+          <t>C001324650</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>C001674440 - FLORES PAICO JOSE SANTOS</t>
+          <t>C001324650 - ULLOA QUEZADA NATIVIDAD VILMA</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H216" s="2" t="n">
@@ -15660,12 +15660,12 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L216" t="inlineStr"/>
@@ -15675,9 +15675,21 @@
         </is>
       </c>
       <c r="N216" t="inlineStr"/>
-      <c r="O216" t="inlineStr"/>
-      <c r="P216" t="inlineStr"/>
-      <c r="Q216" t="inlineStr"/>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -15702,12 +15714,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>C001324650</t>
+          <t>C001735959</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>C001324650 - ULLOA QUEZADA NATIVIDAD VILMA</t>
+          <t>C001735959 - REYES POMA MERCEDES INES</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -15736,25 +15748,13 @@
       <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene espacio sufiente en su celular</t>
         </is>
       </c>
       <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P217" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q217" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -15779,17 +15779,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>C001735959</t>
+          <t>C001324485</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>C001735959 - REYES POMA MERCEDES INES</t>
+          <t>C001324485 - PALOMINO DE PAZ FELICITA LOLA</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H218" s="2" t="n">
@@ -15802,18 +15802,18 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado Definitivamente</t>
         </is>
       </c>
       <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr">
         <is>
-          <t>No tiene espacio sufiente en su celular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N218" t="inlineStr"/>
@@ -15844,12 +15844,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>C001324485</t>
+          <t>C001761601</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>C001324485 - PALOMINO DE PAZ FELICITA LOLA</t>
+          <t>C001761601 - GARCIA ROJAS YAHAIRA XIOMARA</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -15872,7 +15872,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>PDV Cerrado Definitivamente</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L219" t="inlineStr"/>
@@ -16051,17 +16051,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>C001577408</t>
+          <t>C001754218</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>C001577408 - CABRERA LOYOLA DIANA MILY</t>
+          <t>C001754218 - VERDE CAIPO LENY MELISA</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H222" s="2" t="n">
@@ -16074,12 +16074,12 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L222" t="inlineStr"/>
@@ -16089,21 +16089,9 @@
         </is>
       </c>
       <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P222" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q222" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -16128,17 +16116,17 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>C001730237</t>
+          <t>C004051535</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>C001730237 - SALAZAR TORRES CARMEN</t>
+          <t>C004051535 - RAMIREZ VALVERDE ELIZABETH GRACIELA</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H223" s="2" t="n">
@@ -16151,18 +16139,18 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr">
         <is>
-          <t>No usa smartphone</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N223" t="inlineStr"/>
@@ -16193,12 +16181,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>C001732191</t>
+          <t>C001577408</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>C001732191 - ZAVALETA CASTAÑEDA OLGA ELOISA</t>
+          <t>C001577408 - CABRERA LOYOLA DIANA MILY</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -16230,11 +16218,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N224" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr">
         <is>
           <t>Muy dispuesto</t>
@@ -16274,12 +16258,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>C001740647</t>
+          <t>C001730237</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>C001740647 - SILVA DOMINGUEZ MIRIAM</t>
+          <t>C001730237 - SALAZAR TORRES CARMEN</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -16308,25 +16292,13 @@
       <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No usa smartphone</t>
         </is>
       </c>
       <c r="N225" t="inlineStr"/>
-      <c r="O225" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P225" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q225" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -16351,17 +16323,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>C001510834</t>
+          <t>C001732191</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>C001510834 - MENDOZA BENITES DIANA RAQUEL</t>
+          <t>C001732191 - ZAVALETA CASTAÑEDA OLGA ELOISA</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H226" s="2" t="n">
@@ -16374,12 +16346,12 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L226" t="inlineStr"/>
@@ -16388,10 +16360,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N226" t="inlineStr"/>
-      <c r="O226" t="inlineStr"/>
-      <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="inlineStr"/>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -16416,17 +16404,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>C001754218</t>
+          <t>C001740647</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>C001754218 - VERDE CAIPO LENY MELISA</t>
+          <t>C001740647 - SILVA DOMINGUEZ MIRIAM</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H227" s="2" t="n">
@@ -16439,12 +16427,12 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L227" t="inlineStr"/>
@@ -16454,9 +16442,21 @@
         </is>
       </c>
       <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr"/>
-      <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="inlineStr"/>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -16481,12 +16481,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>C004051535</t>
+          <t>C001510834</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>C004051535 - RAMIREZ VALVERDE ELIZABETH GRACIELA</t>
+          <t>C001510834 - MENDOZA BENITES DIANA RAQUEL</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L228" t="inlineStr"/>
@@ -16919,17 +16919,17 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>C004168623</t>
+          <t>C004183506</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>C004168623 - RUBIO DE LA CRUZ GONZALO FELIMON</t>
+          <t>C004183506 - PAREDES VASQUEZ ISABEL NOLBERTA</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H234" s="2" t="n">
@@ -16942,12 +16942,12 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L234" t="inlineStr"/>
@@ -16957,9 +16957,21 @@
         </is>
       </c>
       <c r="N234" t="inlineStr"/>
-      <c r="O234" t="inlineStr"/>
-      <c r="P234" t="inlineStr"/>
-      <c r="Q234" t="inlineStr"/>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Iniciar sesión</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -16984,17 +16996,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>C004183506</t>
+          <t>C004168623</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>C004183506 - PAREDES VASQUEZ ISABEL NOLBERTA</t>
+          <t>C004168623 - RUBIO DE LA CRUZ GONZALO FELIMON</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H235" s="2" t="n">
@@ -17007,12 +17019,12 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L235" t="inlineStr"/>
@@ -17022,21 +17034,9 @@
         </is>
       </c>
       <c r="N235" t="inlineStr"/>
-      <c r="O235" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P235" t="inlineStr">
-        <is>
-          <t>Iniciar sesión</t>
-        </is>
-      </c>
-      <c r="Q235" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr"/>
+      <c r="Q235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -17577,7 +17577,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>HUAMACHUCO</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -17597,12 +17597,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>C001645139</t>
+          <t>C001711172</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>C001645139 - MORILLO ROJAS AMPARO JANET</t>
+          <t>C001711172 - ALONZO GERVACIO AHOLIVANA GESSY</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -17625,7 +17625,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L244" t="inlineStr"/>
@@ -17662,17 +17662,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>C001534280</t>
+          <t>C001285138</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>C001534280 - AGREDA LAIZA DONY DALILA</t>
+          <t>C001285138 - POLO ARANDA DIRSON PAUL</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H245" s="2" t="n">
@@ -17685,12 +17685,12 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L245" t="inlineStr"/>
@@ -17700,14 +17700,26 @@
         </is>
       </c>
       <c r="N245" t="inlineStr"/>
-      <c r="O245" t="inlineStr"/>
-      <c r="P245" t="inlineStr"/>
-      <c r="Q245" t="inlineStr"/>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>HUAMACHUCO</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -17727,12 +17739,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>C001711172</t>
+          <t>C001645139</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>C001711172 - ALONZO GERVACIO AHOLIVANA GESSY</t>
+          <t>C001645139 - MORILLO ROJAS AMPARO JANET</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -17755,7 +17767,7 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L246" t="inlineStr"/>
@@ -17792,17 +17804,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>C001285138</t>
+          <t>C001534280</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>C001285138 - POLO ARANDA DIRSON PAUL</t>
+          <t>C001534280 - AGREDA LAIZA DONY DALILA</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H247" s="2" t="n">
@@ -17815,12 +17827,12 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L247" t="inlineStr"/>
@@ -17830,21 +17842,9 @@
         </is>
       </c>
       <c r="N247" t="inlineStr"/>
-      <c r="O247" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P247" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q247" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O247" t="inlineStr"/>
+      <c r="P247" t="inlineStr"/>
+      <c r="Q247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -18157,12 +18157,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>C001521872</t>
+          <t>C001307309</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>C001521872 - GRAOS BRICENO FREDY RONALD</t>
+          <t>C001307309 - MORALES RAMIREZ JUAN FERNANDO</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -18191,30 +18191,22 @@
       <c r="L252" t="inlineStr"/>
       <c r="M252" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N252" t="inlineStr"/>
-      <c r="O252" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P252" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q252" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+          <t>No abre el app en su celular</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr"/>
+      <c r="P252" t="inlineStr"/>
+      <c r="Q252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>HUAMACHUCO</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -18234,12 +18226,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>C001307309</t>
+          <t>C001455878</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>C001307309 - MORALES RAMIREZ JUAN FERNANDO</t>
+          <t>C001455878 - JULCA NEYRA LUIS JAIME</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -18268,22 +18260,30 @@
       <c r="L253" t="inlineStr"/>
       <c r="M253" t="inlineStr">
         <is>
-          <t>No abre el app en su celular</t>
-        </is>
-      </c>
-      <c r="N253" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O253" t="inlineStr"/>
-      <c r="P253" t="inlineStr"/>
-      <c r="Q253" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr"/>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>HUAMACHUCO</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -18303,17 +18303,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>C001455878</t>
+          <t>C001284684</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>C001455878 - JULCA NEYRA LUIS JAIME</t>
+          <t>C001284684 - OLOYA LAIZA OLGA MARIBEL</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H254" s="2" t="n">
@@ -18326,12 +18326,12 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L254" t="inlineStr"/>
@@ -18341,21 +18341,9 @@
         </is>
       </c>
       <c r="N254" t="inlineStr"/>
-      <c r="O254" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P254" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q254" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O254" t="inlineStr"/>
+      <c r="P254" t="inlineStr"/>
+      <c r="Q254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -18380,12 +18368,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>C001284684</t>
+          <t>C001284814</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>C001284684 - OLOYA LAIZA OLGA MARIBEL</t>
+          <t>C001284814 - RAMIREZ VERA LUZ CELMIRA</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -18408,7 +18396,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L255" t="inlineStr"/>
@@ -18445,17 +18433,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>C001284814</t>
+          <t>C001521872</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>C001284814 - RAMIREZ VERA LUZ CELMIRA</t>
+          <t>C001521872 - GRAOS BRICENO FREDY RONALD</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H256" s="2" t="n">
@@ -18468,12 +18456,12 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L256" t="inlineStr"/>
@@ -18483,9 +18471,21 @@
         </is>
       </c>
       <c r="N256" t="inlineStr"/>
-      <c r="O256" t="inlineStr"/>
-      <c r="P256" t="inlineStr"/>
-      <c r="Q256" t="inlineStr"/>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -18782,17 +18782,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>C004159955</t>
+          <t>C004200910</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>C004159955 - RAMIREZ POLO DALILA ELIZABETH</t>
+          <t>C004200910 - FERNANDEZ REYES JHENIFER VANESSA</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H261" s="2" t="n">
@@ -18805,12 +18805,12 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>PDV Cerrado Definitivamente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L261" t="inlineStr"/>
@@ -18820,9 +18820,21 @@
         </is>
       </c>
       <c r="N261" t="inlineStr"/>
-      <c r="O261" t="inlineStr"/>
-      <c r="P261" t="inlineStr"/>
-      <c r="Q261" t="inlineStr"/>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -18847,17 +18859,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>C004200910</t>
+          <t>C004159955</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>C004200910 - FERNANDEZ REYES JHENIFER VANESSA</t>
+          <t>C004159955 - RAMIREZ POLO DALILA ELIZABETH</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H262" s="2" t="n">
@@ -18870,12 +18882,12 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado Definitivamente</t>
         </is>
       </c>
       <c r="L262" t="inlineStr"/>
@@ -18885,21 +18897,9 @@
         </is>
       </c>
       <c r="N262" t="inlineStr"/>
-      <c r="O262" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P262" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q262" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O262" t="inlineStr"/>
+      <c r="P262" t="inlineStr"/>
+      <c r="Q262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -19196,12 +19196,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>C004183620</t>
+          <t>C004206826</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>C004183620 - RODRIGUEZ TORRES FLORA ARCILA</t>
+          <t>C004206826 - AGREDA RODRIGUEZ MILAGROS DEL PILAR</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -19273,17 +19273,17 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>C004206826</t>
+          <t>C004205760</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>C004206826 - AGREDA RODRIGUEZ MILAGROS DEL PILAR</t>
+          <t>C004205760 - CARRANZA VERDE DORLIN JANEL</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H268" s="2" t="n">
@@ -19296,12 +19296,12 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L268" t="inlineStr"/>
@@ -19311,21 +19311,9 @@
         </is>
       </c>
       <c r="N268" t="inlineStr"/>
-      <c r="O268" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P268" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q268" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O268" t="inlineStr"/>
+      <c r="P268" t="inlineStr"/>
+      <c r="Q268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -19350,12 +19338,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>C004205760</t>
+          <t>C004169642</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>C004205760 - CARRANZA VERDE DORLIN JANEL</t>
+          <t>C004169642 - RODRIGUEZ JAIME SANTOS MARGARITA</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -19415,12 +19403,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>C004169642</t>
+          <t>C004205765</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>C004169642 - RODRIGUEZ JAIME SANTOS MARGARITA</t>
+          <t>C004205765 - BURGOS ULLOA ROSARIO BIRGINIA</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -19480,17 +19468,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>C004205765</t>
+          <t>C004183620</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>C004205765 - BURGOS ULLOA ROSARIO BIRGINIA</t>
+          <t>C004183620 - RODRIGUEZ TORRES FLORA ARCILA</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H271" s="2" t="n">
@@ -19503,12 +19491,12 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L271" t="inlineStr"/>
@@ -19518,9 +19506,21 @@
         </is>
       </c>
       <c r="N271" t="inlineStr"/>
-      <c r="O271" t="inlineStr"/>
-      <c r="P271" t="inlineStr"/>
-      <c r="Q271" t="inlineStr"/>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -19699,12 +19699,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>C001444741</t>
+          <t>C004049198</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>C001444741 - MUNOZ DE PAREDES LUCIA</t>
+          <t>C004049198 - ALFARO YUPANQUI EDUAR NILSON</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -19776,12 +19776,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>C001730849</t>
+          <t>C004102455</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>C001730849 - MEDINA PONCE RUTH NOEMI</t>
+          <t>C004102455 - CORDOVA PENA MARIA MADELEINE</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -19804,7 +19804,7 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L275" t="inlineStr"/>
@@ -19841,12 +19841,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>C004102455</t>
+          <t>C001730849</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>C004102455 - CORDOVA PENA MARIA MADELEINE</t>
+          <t>C001730849 - MEDINA PONCE RUTH NOEMI</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -19869,7 +19869,7 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L276" t="inlineStr"/>
@@ -19906,12 +19906,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>C004049198</t>
+          <t>C001444741</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>C004049198 - ALFARO YUPANQUI EDUAR NILSON</t>
+          <t>C001444741 - MUNOZ DE PAREDES LUCIA</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -20243,17 +20243,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>C001706888</t>
+          <t>C001448981</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>C001706888 - TORRES AGUILAR ALEXANDER ENRIQUE</t>
+          <t>C001448981 - SANDOVAL CRUZ DE GRADOS DAMIANA</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H282" s="2" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>PDV Cerrado Definitivamente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L282" t="inlineStr"/>
@@ -20281,9 +20281,21 @@
         </is>
       </c>
       <c r="N282" t="inlineStr"/>
-      <c r="O282" t="inlineStr"/>
-      <c r="P282" t="inlineStr"/>
-      <c r="Q282" t="inlineStr"/>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -20308,12 +20320,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>C001448981</t>
+          <t>C001408605</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>C001448981 - SANDOVAL CRUZ DE GRADOS DAMIANA</t>
+          <t>C001408605 - SANDOVAL ARANDA ELCIRA</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -20342,25 +20354,13 @@
       <c r="L283" t="inlineStr"/>
       <c r="M283" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No usa apps</t>
         </is>
       </c>
       <c r="N283" t="inlineStr"/>
-      <c r="O283" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P283" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q283" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O283" t="inlineStr"/>
+      <c r="P283" t="inlineStr"/>
+      <c r="Q283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -20385,12 +20385,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>C001521896</t>
+          <t>C001337648</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>C001521896 - VASQUEZ ACOSTA MARIA ROXANI</t>
+          <t>C001337648 - RODRIGUEZ LLARO RICARDINA ASUNCION</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -20419,25 +20419,13 @@
       <c r="L284" t="inlineStr"/>
       <c r="M284" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No maneja celular</t>
         </is>
       </c>
       <c r="N284" t="inlineStr"/>
-      <c r="O284" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P284" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q284" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O284" t="inlineStr"/>
+      <c r="P284" t="inlineStr"/>
+      <c r="Q284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -20462,12 +20450,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>C001408605</t>
+          <t>C001521896</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>C001408605 - SANDOVAL ARANDA ELCIRA</t>
+          <t>C001521896 - VASQUEZ ACOSTA MARIA ROXANI</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -20496,13 +20484,25 @@
       <c r="L285" t="inlineStr"/>
       <c r="M285" t="inlineStr">
         <is>
-          <t>No usa apps</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N285" t="inlineStr"/>
-      <c r="O285" t="inlineStr"/>
-      <c r="P285" t="inlineStr"/>
-      <c r="Q285" t="inlineStr"/>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -20527,17 +20527,17 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>C001337648</t>
+          <t>C001715605</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>C001337648 - RODRIGUEZ LLARO RICARDINA ASUNCION</t>
+          <t>C001715605 - MULTISERVICIOS MANOTAS E.I.R.L.</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H286" s="2" t="n">
@@ -20550,18 +20550,18 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado Definitivamente</t>
         </is>
       </c>
       <c r="L286" t="inlineStr"/>
       <c r="M286" t="inlineStr">
         <is>
-          <t>No maneja celular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N286" t="inlineStr"/>
@@ -20592,12 +20592,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>C001715605</t>
+          <t>C001706888</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>C001715605 - MULTISERVICIOS MANOTAS E.I.R.L.</t>
+          <t>C001706888 - TORRES AGUILAR ALEXANDER ENRIQUE</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -20852,17 +20852,17 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>C001734919</t>
+          <t>C001128320</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>C001734919 - FIGUEROA RAZA ELIZABETH</t>
+          <t>C001128320 - RODRIGUEZ GARCIA YANIRA EDITH</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H291" s="2" t="n">
@@ -20875,12 +20875,12 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L291" t="inlineStr"/>
@@ -20890,9 +20890,21 @@
         </is>
       </c>
       <c r="N291" t="inlineStr"/>
-      <c r="O291" t="inlineStr"/>
-      <c r="P291" t="inlineStr"/>
-      <c r="Q291" t="inlineStr"/>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -20917,17 +20929,17 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>C001731621</t>
+          <t>C001641758</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>C001731621 - AGREDA ALZA LIDIA ANABELLA</t>
+          <t>C001641758 - QUISPE ARMAS CARLOS HUMBERTO</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H292" s="2" t="n">
@@ -20940,12 +20952,12 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L292" t="inlineStr"/>
@@ -20954,7 +20966,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N292" t="inlineStr"/>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="O292" t="inlineStr"/>
       <c r="P292" t="inlineStr"/>
       <c r="Q292" t="inlineStr"/>
@@ -20982,12 +20998,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>C001641758</t>
+          <t>C001674629</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>C001641758 - QUISPE ARMAS CARLOS HUMBERTO</t>
+          <t>C001674629 - VASQUEZ MENDEZ HILDA PALMIRA</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -21019,14 +21035,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N293" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O293" t="inlineStr"/>
-      <c r="P293" t="inlineStr"/>
-      <c r="Q293" t="inlineStr"/>
+      <c r="N293" t="inlineStr"/>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -21051,17 +21075,17 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>C001674629</t>
+          <t>C001734919</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>C001674629 - VASQUEZ MENDEZ HILDA PALMIRA</t>
+          <t>C001734919 - FIGUEROA RAZA ELIZABETH</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H294" s="2" t="n">
@@ -21074,12 +21098,12 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L294" t="inlineStr"/>
@@ -21089,21 +21113,9 @@
         </is>
       </c>
       <c r="N294" t="inlineStr"/>
-      <c r="O294" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P294" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q294" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O294" t="inlineStr"/>
+      <c r="P294" t="inlineStr"/>
+      <c r="Q294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -21128,17 +21140,17 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>C001128320</t>
+          <t>C001731621</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>C001128320 - RODRIGUEZ GARCIA YANIRA EDITH</t>
+          <t>C001731621 - AGREDA ALZA LIDIA ANABELLA</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H295" s="2" t="n">
@@ -21151,12 +21163,12 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L295" t="inlineStr"/>
@@ -21166,21 +21178,9 @@
         </is>
       </c>
       <c r="N295" t="inlineStr"/>
-      <c r="O295" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P295" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q295" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O295" t="inlineStr"/>
+      <c r="P295" t="inlineStr"/>
+      <c r="Q295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -21270,12 +21270,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>C004167428</t>
+          <t>C004060767</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>C004167428 - RODRIGUEZ CORVERA JAYER LUIS</t>
+          <t>C004060767 - VEGA ARGOMEDO LUIS ALBERTO</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -21308,9 +21308,21 @@
         </is>
       </c>
       <c r="N297" t="inlineStr"/>
-      <c r="O297" t="inlineStr"/>
-      <c r="P297" t="inlineStr"/>
-      <c r="Q297" t="inlineStr"/>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -21335,12 +21347,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>C004060767</t>
+          <t>C004167428</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>C004060767 - VEGA ARGOMEDO LUIS ALBERTO</t>
+          <t>C004167428 - RODRIGUEZ CORVERA JAYER LUIS</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -21373,21 +21385,9 @@
         </is>
       </c>
       <c r="N298" t="inlineStr"/>
-      <c r="O298" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P298" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q298" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O298" t="inlineStr"/>
+      <c r="P298" t="inlineStr"/>
+      <c r="Q298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -21554,17 +21554,17 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>C001640733</t>
+          <t>C001691955</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>C001640733 - PRETELL CORDOVA EVELYN JANNETH</t>
+          <t>C001691955 - MELCHOR GERONIMO KELI MEDALIT</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H301" s="2" t="n">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L301" t="inlineStr"/>
@@ -21592,21 +21592,9 @@
         </is>
       </c>
       <c r="N301" t="inlineStr"/>
-      <c r="O301" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P301" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q301" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O301" t="inlineStr"/>
+      <c r="P301" t="inlineStr"/>
+      <c r="Q301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -21631,12 +21619,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>C001691955</t>
+          <t>C001689022</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>C001691955 - MELCHOR GERONIMO KELI MEDALIT</t>
+          <t>C001689022 - MIRANDA SAAVEDRA DEYSY JOHANA</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -21696,17 +21684,17 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>C001689022</t>
+          <t>C001640733</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>C001689022 - MIRANDA SAAVEDRA DEYSY JOHANA</t>
+          <t>C001640733 - PRETELL CORDOVA EVELYN JANNETH</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H303" s="2" t="n">
@@ -21719,12 +21707,12 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L303" t="inlineStr"/>
@@ -21734,9 +21722,21 @@
         </is>
       </c>
       <c r="N303" t="inlineStr"/>
-      <c r="O303" t="inlineStr"/>
-      <c r="P303" t="inlineStr"/>
-      <c r="Q303" t="inlineStr"/>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -21761,12 +21761,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>C004241784</t>
+          <t>C004240756</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>C004241784 - RAMOS VALENCIA CONSUELO HAYDEE</t>
+          <t>C004240756 - ESCOBAL RAMOS MONICA JULISSA</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -21838,12 +21838,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>C004244367</t>
+          <t>C004241784</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>C004244367 - TORIBIO HONORIO LIZ VERONICA</t>
+          <t>C004241784 - RAMOS VALENCIA CONSUELO HAYDEE</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -21872,13 +21872,25 @@
       <c r="L305" t="inlineStr"/>
       <c r="M305" t="inlineStr">
         <is>
-          <t>No hay promociones, prefere comprar en el mayorista</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N305" t="inlineStr"/>
-      <c r="O305" t="inlineStr"/>
-      <c r="P305" t="inlineStr"/>
-      <c r="Q305" t="inlineStr"/>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -21903,12 +21915,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>C004240756</t>
+          <t>C004244367</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>C004240756 - ESCOBAL RAMOS MONICA JULISSA</t>
+          <t>C004244367 - TORIBIO HONORIO LIZ VERONICA</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -21937,25 +21949,13 @@
       <c r="L306" t="inlineStr"/>
       <c r="M306" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No hay promociones, prefere comprar en el mayorista</t>
         </is>
       </c>
       <c r="N306" t="inlineStr"/>
-      <c r="O306" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P306" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q306" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O306" t="inlineStr"/>
+      <c r="P306" t="inlineStr"/>
+      <c r="Q306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -22057,17 +22057,17 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>C001634973</t>
+          <t>C004241592</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>C001634973 - FLOREANO ALFARO AUGUSTO ENRIQUE</t>
+          <t>C004241592 - ASPIROS GUILLEN SILBESTRE</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H308" s="2" t="n">
@@ -22080,12 +22080,12 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L308" t="inlineStr"/>
@@ -22095,21 +22095,9 @@
         </is>
       </c>
       <c r="N308" t="inlineStr"/>
-      <c r="O308" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P308" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q308" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O308" t="inlineStr"/>
+      <c r="P308" t="inlineStr"/>
+      <c r="Q308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -22134,17 +22122,17 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>C001617486</t>
+          <t>C004242198</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>C001617486 - MORALES MENDEZ HILDER LEONARDO</t>
+          <t>C004242198 - ALFARO FLORES MILAGROS AMPARO</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H309" s="2" t="n">
@@ -22157,12 +22145,12 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>PDV Cerrado Definitivamente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L309" t="inlineStr"/>
@@ -22172,9 +22160,21 @@
         </is>
       </c>
       <c r="N309" t="inlineStr"/>
-      <c r="O309" t="inlineStr"/>
-      <c r="P309" t="inlineStr"/>
-      <c r="Q309" t="inlineStr"/>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -22199,17 +22199,17 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>C004242198</t>
+          <t>C001617486</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>C004242198 - ALFARO FLORES MILAGROS AMPARO</t>
+          <t>C001617486 - MORALES MENDEZ HILDER LEONARDO</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H310" s="2" t="n">
@@ -22222,12 +22222,12 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado Definitivamente</t>
         </is>
       </c>
       <c r="L310" t="inlineStr"/>
@@ -22237,21 +22237,9 @@
         </is>
       </c>
       <c r="N310" t="inlineStr"/>
-      <c r="O310" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P310" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q310" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O310" t="inlineStr"/>
+      <c r="P310" t="inlineStr"/>
+      <c r="Q310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -22276,17 +22264,17 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>C004241592</t>
+          <t>C001634973</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>C004241592 - ASPIROS GUILLEN SILBESTRE</t>
+          <t>C001634973 - FLOREANO ALFARO AUGUSTO ENRIQUE</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H311" s="2" t="n">
@@ -22299,12 +22287,12 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L311" t="inlineStr"/>
@@ -22314,9 +22302,21 @@
         </is>
       </c>
       <c r="N311" t="inlineStr"/>
-      <c r="O311" t="inlineStr"/>
-      <c r="P311" t="inlineStr"/>
-      <c r="Q311" t="inlineStr"/>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -22548,12 +22548,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>C001122173</t>
+          <t>C001216214</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>C001122173 - ESTEBAN POLO MARIA</t>
+          <t>C001216214 - MALDONADO TRUJILLO DE VILLARREAL ASUNCIO</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -22625,17 +22625,17 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>C001122249</t>
+          <t>C001122173</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>C001122249 - SALINAS CRUZ DE FLOREANO ELCIRA AZUCENA</t>
+          <t>C001122173 - ESTEBAN POLO MARIA</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H316" s="2" t="n">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L316" t="inlineStr"/>
@@ -22663,9 +22663,21 @@
         </is>
       </c>
       <c r="N316" t="inlineStr"/>
-      <c r="O316" t="inlineStr"/>
-      <c r="P316" t="inlineStr"/>
-      <c r="Q316" t="inlineStr"/>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -22690,17 +22702,17 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>C001216214</t>
+          <t>C001122249</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>C001216214 - MALDONADO TRUJILLO DE VILLARREAL ASUNCIO</t>
+          <t>C001122249 - SALINAS CRUZ DE FLOREANO ELCIRA AZUCENA</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H317" s="2" t="n">
@@ -22713,12 +22725,12 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L317" t="inlineStr"/>
@@ -22728,21 +22740,9 @@
         </is>
       </c>
       <c r="N317" t="inlineStr"/>
-      <c r="O317" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P317" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q317" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O317" t="inlineStr"/>
+      <c r="P317" t="inlineStr"/>
+      <c r="Q317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>C001345662</t>
+          <t>C001326631</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>C001345662 - MAURICIO DE LA CRUZ EUGENIA</t>
+          <t>C001326631 - ESQUIVEL DE SANCHEZ JUANA</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -22801,25 +22801,13 @@
       <c r="L318" t="inlineStr"/>
       <c r="M318" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No usa celular</t>
         </is>
       </c>
       <c r="N318" t="inlineStr"/>
-      <c r="O318" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P318" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q318" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O318" t="inlineStr"/>
+      <c r="P318" t="inlineStr"/>
+      <c r="Q318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -22844,12 +22832,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>C001326631</t>
+          <t>C001345662</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>C001326631 - ESQUIVEL DE SANCHEZ JUANA</t>
+          <t>C001345662 - MAURICIO DE LA CRUZ EUGENIA</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -22878,13 +22866,25 @@
       <c r="L319" t="inlineStr"/>
       <c r="M319" t="inlineStr">
         <is>
-          <t>No usa celular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N319" t="inlineStr"/>
-      <c r="O319" t="inlineStr"/>
-      <c r="P319" t="inlineStr"/>
-      <c r="Q319" t="inlineStr"/>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -22986,17 +22986,17 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>C001129172</t>
+          <t>C001348035</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>C001129172 - ROBLES ESPEJO PEDRO</t>
+          <t>C001348035 - AGUILAR GUTIERREZ ELICET SUSAN</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H321" s="2" t="n">
@@ -23009,12 +23009,12 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L321" t="inlineStr"/>
@@ -23024,21 +23024,9 @@
         </is>
       </c>
       <c r="N321" t="inlineStr"/>
-      <c r="O321" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P321" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q321" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O321" t="inlineStr"/>
+      <c r="P321" t="inlineStr"/>
+      <c r="Q321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -23270,17 +23258,17 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>C001348035</t>
+          <t>C001129172</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>C001348035 - AGUILAR GUTIERREZ ELICET SUSAN</t>
+          <t>C001129172 - ROBLES ESPEJO PEDRO</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H325" s="2" t="n">
@@ -23293,12 +23281,12 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L325" t="inlineStr"/>
@@ -23308,9 +23296,21 @@
         </is>
       </c>
       <c r="N325" t="inlineStr"/>
-      <c r="O325" t="inlineStr"/>
-      <c r="P325" t="inlineStr"/>
-      <c r="Q325" t="inlineStr"/>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">

--- a/excel/distribuidora-sol-del-valle-s-a-c_efectivos.xlsx
+++ b/excel/distribuidora-sol-del-valle-s-a-c_efectivos.xlsx
@@ -563,17 +563,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C001345662</t>
+          <t>C001348035</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C001345662 - MAURICIO DE LA CRUZ EUGENIA</t>
+          <t>C001348035 - AGUILAR GUTIERREZ ELICET SUSAN</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
@@ -586,12 +586,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -601,21 +601,9 @@
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -640,12 +628,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C001121497</t>
+          <t>C001711582</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C001121497 - REYES CUEVA ELSA NATALIA</t>
+          <t>C001711582 - OTINIANO LOZANO SANDRA GREGORIA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -668,7 +656,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -705,12 +693,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C001396749</t>
+          <t>C001626791</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C001396749 - FLORES ROSALES JUANITA JULIA</t>
+          <t>C001626791 - RAMIREZ BERNABE JEAN POOL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -755,7 +743,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
     </row>
@@ -767,7 +755,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -782,12 +770,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C001405781</t>
+          <t>C001612867</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C001405781 - ARAUJO AGUILAR KELLER MARJORIE</t>
+          <t>C001612867 - DIAZ RAFAEL ERIKA MARIVI</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -832,7 +820,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más capacitación</t>
         </is>
       </c>
     </row>
@@ -859,17 +847,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C001348035</t>
+          <t>C001121500</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C001348035 - AGUILAR GUTIERREZ ELICET SUSAN</t>
+          <t>C001121500 - MERINO VARGAS GERARDO MELQUIADES</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
@@ -882,18 +870,18 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No us apps</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -924,12 +912,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C001121500</t>
+          <t>C001345662</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C001121500 - MERINO VARGAS GERARDO MELQUIADES</t>
+          <t>C001345662 - MAURICIO DE LA CRUZ EUGENIA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -958,13 +946,25 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>No us apps</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -989,17 +989,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C001612867</t>
+          <t>C001121497</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C001612867 - DIAZ RAFAEL ERIKA MARIVI</t>
+          <t>C001121497 - REYES CUEVA ELSA NATALIA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1027,21 +1027,9 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Más capacitación</t>
-        </is>
-      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1066,17 +1054,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C001122249</t>
+          <t>C001396749</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C001122249 - SALINAS CRUZ DE FLOREANO ELCIRA AZUCENA</t>
+          <t>C001396749 - FLORES ROSALES JUANITA JULIA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
@@ -1089,12 +1077,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1104,9 +1092,21 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C001398311</t>
+          <t>C001405781</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C001398311 - ARAUJO QUILICHE ANA CLAIRE</t>
+          <t>C001405781 - ARAUJO AGUILAR KELLER MARJORIE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1208,17 +1208,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C001626791</t>
+          <t>C001122249</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C001626791 - RAMIREZ BERNABE JEAN POOL</t>
+          <t>C001122249 - SALINAS CRUZ DE FLOREANO ELCIRA AZUCENA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1246,21 +1246,9 @@
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1285,17 +1273,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C001711582</t>
+          <t>C001398311</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C001711582 - OTINIANO LOZANO SANDRA GREGORIA</t>
+          <t>C001398311 - ARAUJO QUILICHE ANA CLAIRE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
@@ -1308,12 +1296,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1323,9 +1311,21 @@
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C004175425</t>
+          <t>C001391863</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C004175425 - GERMAN MENDIETA ANA MARIA</t>
+          <t>C001391863 - REYES RAVELO NORMA MARIBEL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C004171310</t>
+          <t>C001326631</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C004171310 - BURGOS FERNANDEZ ROBERTO JAVIER</t>
+          <t>C001326631 - ESQUIVEL DE SANCHEZ JUANA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
@@ -1438,18 +1438,18 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No usa celular</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C001326631</t>
+          <t>C004050172</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C001326631 - ESQUIVEL DE SANCHEZ JUANA</t>
+          <t>C004050172 - RODRIGUEZ VASQUEZ ROSARIO ANGELICA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1514,13 +1514,25 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>No usa celular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1545,12 +1557,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>C004050172</t>
+          <t>C004167425</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C004050172 - RODRIGUEZ VASQUEZ ROSARIO ANGELICA</t>
+          <t>C004167425 - FELIPE BAZAN DE ROJAS BETTY MARUJA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1607,7 +1619,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1622,17 +1634,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C001727752</t>
+          <t>C001121516</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C001727752 - SANCHEZ GARCIA NAYELY LORENA</t>
+          <t>C001121516 - ROMERO ENRIQUEZ ANGEL FELIZARDO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
@@ -1645,18 +1657,18 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No usa apps</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1672,7 +1684,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1687,17 +1699,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C001767433</t>
+          <t>C001727752</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C001767433 - RODRIGUEZ BEJARANO SEGUNDO EUSEBIO</t>
+          <t>C001727752 - SANCHEZ GARCIA NAYELY LORENA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
@@ -1710,12 +1722,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1725,21 +1737,9 @@
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1764,17 +1764,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C001121516</t>
+          <t>C004175425</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C001121516 - ROMERO ENRIQUEZ ANGEL FELIZARDO</t>
+          <t>C004175425 - GERMAN MENDIETA ANA MARIA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
@@ -1787,18 +1787,18 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>No usa apps</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C001391863</t>
+          <t>C004171310</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C001391863 - REYES RAVELO NORMA MARIBEL</t>
+          <t>C004171310 - BURGOS FERNANDEZ ROBERTO JAVIER</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1971,12 +1971,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>C004192601</t>
+          <t>C001767433</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C004192601 - CARLOS RODRIGUEZ MARLENI LUZVENI</t>
+          <t>C001767433 - RODRIGUEZ BEJARANO SEGUNDO EUSEBIO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2048,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>C004167425</t>
+          <t>C004192601</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C004167425 - FELIPE BAZAN DE ROJAS BETTY MARUJA</t>
+          <t>C004192601 - CARLOS RODRIGUEZ MARLENI LUZVENI</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2799,17 +2799,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>C004190849</t>
+          <t>C001737108</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C004190849 - VALVERDE ULLOA SANTOS AGUSTINA</t>
+          <t>C001737108 - CABRERA LUCAS SEGUNDO TIMOTEO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2836,26 +2836,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2880,12 +2864,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>C001121527</t>
+          <t>C001737111</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C001121527 - CASTRO DE RODRIGUEZ SUSANA FRANCISCA</t>
+          <t>C001737111 - SAUNA CORCUERA LIDIA EDELGUISA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2914,14 +2898,10 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>No usa celular</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>No desea usar apps</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
@@ -2949,17 +2929,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>C001737108</t>
+          <t>C004190849</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C001737108 - CABRERA LUCAS SEGUNDO TIMOTEO</t>
+          <t>C004190849 - VALVERDE ULLOA SANTOS AGUSTINA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
@@ -2972,12 +2952,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2986,10 +2966,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3014,12 +3010,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>C001737111</t>
+          <t>C001121527</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C001737111 - SAUNA CORCUERA LIDIA EDELGUISA</t>
+          <t>C001121527 - CASTRO DE RODRIGUEZ SUSANA FRANCISCA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3048,10 +3044,14 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>No desea usar apps</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>No usa celular</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>C004190462</t>
+          <t>C001762133</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C004190462 - TANTALEAN LAYZA RAQUEL PATRICIA</t>
+          <t>C001762133 - LOPEZ MORENO YURI LISETH</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3144,12 +3144,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>C001559213</t>
+          <t>C001572723</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C001559213 - RUIZ ESPINOZA DELIA ISABEL</t>
+          <t>C001572723 - LIÑAN TORRES ASUNCION ROSMERY</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>C001640494</t>
+          <t>C004190462</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C001640494 - PEREZ FLORES HAYDEE EDITH</t>
+          <t>C004190462 - TANTALEAN LAYZA RAQUEL PATRICIA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>C001762133</t>
+          <t>C001559213</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C001762133 - LOPEZ MORENO YURI LISETH</t>
+          <t>C001559213 - RUIZ ESPINOZA DELIA ISABEL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -3324,9 +3324,21 @@
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3351,17 +3363,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>C001572723</t>
+          <t>C001640494</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C001572723 - LIÑAN TORRES ASUNCION ROSMERY</t>
+          <t>C001640494 - PEREZ FLORES HAYDEE EDITH</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
@@ -3374,12 +3386,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -3389,21 +3401,9 @@
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3428,17 +3428,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>C001526540</t>
+          <t>C001429931</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C001526540 - FLORES BRICEÑO MARIA DOLORES</t>
+          <t>C001429931 - IBANEZ VASQUEZ PAZ FELICIANA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
@@ -3451,25 +3451,21 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>No se pudo por bateria</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
@@ -3497,17 +3493,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>C001739408</t>
+          <t>C001745416</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C001739408 - CHAVEZ SANTA CRUZ VANESSA XIOMARA</t>
+          <t>C001745416 - CASTILLO HARO RICARDO ALEXANDER</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
@@ -3520,25 +3516,21 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Tiene iphone</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
@@ -3566,17 +3558,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>C001745416</t>
+          <t>C001676127</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C001745416 - CASTILLO HARO RICARDO ALEXANDER</t>
+          <t>C001676127 - ESCOVEDO AREDO ANITA ANDREA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
@@ -3589,12 +3581,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -3604,9 +3596,21 @@
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3631,17 +3635,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>C001468666</t>
+          <t>C001387670</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C001468666 - VEGA QUISPE ERICK JOEL</t>
+          <t>C001387670 - CIEZA SOTO MANUELA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H46" s="2" t="n">
@@ -3654,18 +3658,18 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No usa celular</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -3696,17 +3700,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>C001524645</t>
+          <t>C001167763</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C001524645 - MELENDEZ PEREZ DODIT</t>
+          <t>C001167763 - MORI BARTOLOME ANA ISABEL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
@@ -3719,12 +3723,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3734,9 +3738,21 @@
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3761,17 +3777,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>C001429931</t>
+          <t>C001436632</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C001429931 - IBANEZ VASQUEZ PAZ FELICIANA</t>
+          <t>C001436632 - MORENO TORRES HERLINDA NOEMI</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
@@ -3784,21 +3800,25 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>No usa apps</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
@@ -3826,17 +3846,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>C001364499</t>
+          <t>C001468666</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C001364499 - BURGOS DE QUISPE OLGA DALILA</t>
+          <t>C001468666 - VEGA QUISPE ERICK JOEL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
@@ -3849,12 +3869,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -3864,21 +3884,9 @@
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3903,12 +3911,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>C001389462</t>
+          <t>C001524645</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C001389462 - PESANTES ARQUEROS GRETY RENY</t>
+          <t>C001524645 - MELENDEZ PEREZ DODIT</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3953,7 +3961,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3968,12 +3976,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>C001409233</t>
+          <t>C001526540</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C001409233 - VERA CRUZ NATHALY SAMANTHA</t>
+          <t>C001526540 - FLORES BRICEÑO MARIA DOLORES</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4002,25 +4010,17 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+          <t>No se pudo por bateria</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>C001167763</t>
+          <t>C001364499</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C001167763 - MORI BARTOLOME ANA ISABEL</t>
+          <t>C001364499 - BURGOS DE QUISPE OLGA DALILA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
     </row>
@@ -4122,17 +4122,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>C001387670</t>
+          <t>C001389462</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C001387670 - CIEZA SOTO MANUELA</t>
+          <t>C001389462 - PESANTES ARQUEROS GRETY RENY</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
@@ -4145,18 +4145,18 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>No usa celular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>C001676127</t>
+          <t>C001409233</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C001676127 - ESCOVEDO AREDO ANITA ANDREA</t>
+          <t>C001409233 - VERA CRUZ NATHALY SAMANTHA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>C001436632</t>
+          <t>C001739408</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C001436632 - MORENO TORRES HERLINDA NOEMI</t>
+          <t>C001739408 - CHAVEZ SANTA CRUZ VANESSA XIOMARA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4298,7 +4298,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>No usa apps</t>
+          <t>Tiene iphone</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>C001760417</t>
+          <t>C004048840</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>C001760417 - BOCANEGRA HILARIO JHOORDYN AQUILES</t>
+          <t>C004048840 - CORTIJO NEYRA LUCERO DEL CIELO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4373,7 +4373,7 @@
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -4410,12 +4410,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>C004184682</t>
+          <t>C001717735</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>C004184682 - SUAREZ RODRIGUEZ LEONEL</t>
+          <t>C001717735 - CASTAÑEDA CASTILLO JULIO CESAR</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -4475,17 +4475,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>C001717735</t>
+          <t>C001760417</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C001717735 - CASTAÑEDA CASTILLO JULIO CESAR</t>
+          <t>C001760417 - BOCANEGRA HILARIO JHOORDYN AQUILES</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H58" s="2" t="n">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -4513,9 +4513,21 @@
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4540,17 +4552,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>C004048840</t>
+          <t>C004184682</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C004048840 - CORTIJO NEYRA LUCERO DEL CIELO</t>
+          <t>C004184682 - SUAREZ RODRIGUEZ LEONEL</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H59" s="2" t="n">
@@ -4563,12 +4575,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -4578,21 +4590,9 @@
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4617,12 +4617,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>C004185437</t>
+          <t>C004197221</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C004185437 - ZAVALETA BAYLON PAOLA NOEMI</t>
+          <t>C004197221 - VARGAS REYES ARCADIO MODESTO</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>C004197150</t>
+          <t>C004185437</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C004197150 - PONCE DOMINGUEZ MARIA PILAR</t>
+          <t>C004185437 - ZAVALETA BAYLON PAOLA NOEMI</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>C004197221</t>
+          <t>C004197150</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C004197221 - VARGAS REYES ARCADIO MODESTO</t>
+          <t>C004197150 - PONCE DOMINGUEZ MARIA PILAR</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>C001733660</t>
+          <t>C001331144</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>C001733660 - MIRANDA VARGAS MARIA YSABEL</t>
+          <t>C001331144 - INFANTES CHACON YOLANDA MARINA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -4925,12 +4925,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>C001639514</t>
+          <t>C001628609</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>C001639514 - SANCHEZ PEREZ MARITZA ISELA</t>
+          <t>C001628609 - RODRIGUEZ ROBLES ALBERTO ROGER</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4990,12 +4990,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>C001513040</t>
+          <t>C001331147</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C001513040 - ACOSTA FERNANDEZ MARCELINA ESTHER</t>
+          <t>C001331147 - PEREZ ESQUIVEL ANITA RAQUEL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>C001512631</t>
+          <t>C001333647</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C001512631 - LOPEZ CHAVEZ YAQUELIN PATRICIA</t>
+          <t>C001333647 - GALLARDO BARRETO JORGE LUIS</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5101,7 +5101,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>No tiene celulae</t>
+          <t>No desea usar apps</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -5132,12 +5132,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>C001331144</t>
+          <t>C001513040</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C001331144 - INFANTES CHACON YOLANDA MARINA</t>
+          <t>C001513040 - ACOSTA FERNANDEZ MARCELINA ESTHER</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5209,17 +5209,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>C001628609</t>
+          <t>C001512631</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>C001628609 - RODRIGUEZ ROBLES ALBERTO ROGER</t>
+          <t>C001512631 - LOPEZ CHAVEZ YAQUELIN PATRICIA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H68" s="2" t="n">
@@ -5232,18 +5232,18 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene celulae</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -5274,17 +5274,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>C001683933</t>
+          <t>C001733660</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>C001683933 - ARMAS DIAZ FAUSTA MERCEDES</t>
+          <t>C001733660 - MIRANDA VARGAS MARIA YSABEL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H69" s="2" t="n">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -5312,9 +5312,21 @@
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5339,17 +5351,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>C001732698</t>
+          <t>C001639514</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>C001732698 - TICLIAHUANCA REYNA MARILYN FLORENCIA</t>
+          <t>C001639514 - SANCHEZ PEREZ MARITZA ISELA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H70" s="2" t="n">
@@ -5362,12 +5374,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -5377,21 +5389,9 @@
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>C001331142</t>
+          <t>C001669043</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C001331142 - FERREL LOPEZ DE LAZARO TOMASA TERESA</t>
+          <t>C001669043 - ORBEGOSO MUÑOZ EMELDA ELIZABETH</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>C001674351</t>
+          <t>C001331346</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>C001674351 - YSIDRO SOCORRO ANELIDA</t>
+          <t>C001331346 - LOPEZ POLO MARIA FLORENCIA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5570,17 +5570,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>C001661625</t>
+          <t>C001331347</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>C001661625 - RODRIGUEZ HORNA ELENA MARI</t>
+          <t>C001331347 - FARROÑAN BALDERA BALTAZARA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H73" s="2" t="n">
@@ -5593,25 +5593,21 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Usa iphone</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
@@ -5639,12 +5635,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>C001331147</t>
+          <t>C001483227</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C001331147 - PEREZ ESQUIVEL ANITA RAQUEL</t>
+          <t>C001483227 - VILLANUEVA HILARIO CYNTHIA YESENIA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5689,7 +5685,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
     </row>
@@ -5716,17 +5712,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>C001333647</t>
+          <t>C001735407</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C001333647 - GALLARDO BARRETO JORGE LUIS</t>
+          <t>C001735407 - GUTIERREZ ROSALES PEDRO MARCOS</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H75" s="2" t="n">
@@ -5739,18 +5735,18 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>No desea usar apps</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -5766,7 +5762,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5781,12 +5777,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>C001331346</t>
+          <t>C001661625</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C001331346 - LOPEZ POLO MARIA FLORENCIA</t>
+          <t>C001661625 - RODRIGUEZ HORNA ELENA MARI</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5815,25 +5811,17 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+          <t>Usa iphone</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5858,17 +5846,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>C001331347</t>
+          <t>C001674351</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C001331347 - FARROÑAN BALDERA BALTAZARA</t>
+          <t>C001674351 - YSIDRO SOCORRO ANELIDA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H77" s="2" t="n">
@@ -5881,12 +5869,12 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -5896,9 +5884,21 @@
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5923,17 +5923,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>C001483227</t>
+          <t>C001683933</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>C001483227 - VILLANUEVA HILARIO CYNTHIA YESENIA</t>
+          <t>C001683933 - ARMAS DIAZ FAUSTA MERCEDES</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H78" s="2" t="n">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -5961,21 +5961,9 @@
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5985,7 +5973,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6000,12 +5988,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>C001669043</t>
+          <t>C001732698</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>C001669043 - ORBEGOSO MUÑOZ EMELDA ELIZABETH</t>
+          <t>C001732698 - TICLIAHUANCA REYNA MARILYN FLORENCIA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6050,7 +6038,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
     </row>
@@ -6077,17 +6065,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>C001735407</t>
+          <t>C001331142</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>C001735407 - GUTIERREZ ROSALES PEDRO MARCOS</t>
+          <t>C001331142 - FERREL LOPEZ DE LAZARO TOMASA TERESA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H80" s="2" t="n">
@@ -6100,12 +6088,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -6115,9 +6103,21 @@
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>C001679465</t>
+          <t>C004168484</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>C001679465 - LAUREANO QUEZADA EVELYN NOEMI</t>
+          <t>C004168484 - ROJAS POLO LISBETH SANTA ANA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -6272,17 +6272,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>C001678739</t>
+          <t>C001563276</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>C001678739 - AVILA PELAEZ ISAI ALDAHIR</t>
+          <t>C001563276 - MENDEZ MENDEZ DEROMILDA</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H83" s="2" t="n">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -6310,9 +6310,21 @@
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6337,12 +6349,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>C001126145</t>
+          <t>C001678739</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>C001126145 - AREDO QUISPE EDDIN EDGAR</t>
+          <t>C001678739 - AVILA PELAEZ ISAI ALDAHIR</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6387,7 +6399,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6402,17 +6414,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>C004059726</t>
+          <t>C001679465</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>C004059726 - GERONIMO PEREZ MARINO</t>
+          <t>C001679465 - LAUREANO QUEZADA EVELYN NOEMI</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H85" s="2" t="n">
@@ -6425,12 +6437,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -6440,21 +6452,9 @@
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6479,17 +6479,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>C004168484</t>
+          <t>C001629991</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>C004168484 - ROJAS POLO LISBETH SANTA ANA</t>
+          <t>C001629991 - AVILA RODRIGUEZ LADY ROSSELLI</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H86" s="2" t="n">
@@ -6502,12 +6502,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -6517,9 +6517,21 @@
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Iniciar sesión</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6544,12 +6556,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>C001563276</t>
+          <t>C004059726</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>C001563276 - MENDEZ MENDEZ DEROMILDA</t>
+          <t>C004059726 - GERONIMO PEREZ MARINO</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6621,12 +6633,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>C004172178</t>
+          <t>C001126145</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>C004172178 - CRUZ RODRIGUEZ ADRIANA MILAGROS</t>
+          <t>C001126145 - AREDO QUISPE EDDIN EDGAR</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6686,17 +6698,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>C004054693</t>
+          <t>C004172178</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>C004054693 - VASQUEZ VALDERRAMA SARA</t>
+          <t>C004172178 - CRUZ RODRIGUEZ ADRIANA MILAGROS</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H89" s="2" t="n">
@@ -6709,12 +6721,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -6724,21 +6736,9 @@
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6763,17 +6763,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>C004059712</t>
+          <t>C004054693</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>C004059712 - GAMBOA AVILA FLORCITA BETTY</t>
+          <t>C004054693 - VASQUEZ VALDERRAMA SARA</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H90" s="2" t="n">
@@ -6786,12 +6786,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>PDV Cerrado Definitivamente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -6801,9 +6801,21 @@
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6813,7 +6825,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6828,17 +6840,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>C001618305</t>
+          <t>C004059712</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>C001618305 - MOGOLLON GARCIA JORGE LUIS</t>
+          <t>C004059712 - GAMBOA AVILA FLORCITA BETTY</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H91" s="2" t="n">
@@ -6851,12 +6863,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado Definitivamente</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -6866,21 +6878,9 @@
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6905,12 +6905,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>C001392282</t>
+          <t>C001576999</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>C001392282 - POLO CRUZ JOSE SANTOS</t>
+          <t>C001576999 - TORRES LIZARRAGA GIANMARCO ANDRE</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
     </row>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>C001475142</t>
+          <t>C001703145</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>C001475142 - VELARDE RAMOS MELVITA YOMAR</t>
+          <t>C001703145 - GONZALES ZAVALETA YORLIN DARLIN</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -7047,17 +7047,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>C001504996</t>
+          <t>C001711464</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>C001504996 - SALDAÑA NAVARRO JENY JUDITH</t>
+          <t>C001711464 - DIONICIO HERNANDEZ MIRTA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H94" s="2" t="n">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -7085,9 +7085,21 @@
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7097,7 +7109,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -7112,12 +7124,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>C001711464</t>
+          <t>C001618305</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>C001711464 - DIONICIO HERNANDEZ MIRTA</t>
+          <t>C001618305 - MOGOLLON GARCIA JORGE LUIS</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7162,7 +7174,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
     </row>
@@ -7189,12 +7201,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>C001576999</t>
+          <t>C001392282</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>C001576999 - TORRES LIZARRAGA GIANMARCO ANDRE</t>
+          <t>C001392282 - POLO CRUZ JOSE SANTOS</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7239,7 +7251,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -7266,12 +7278,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>C001703145</t>
+          <t>C001475142</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>C001703145 - GONZALES ZAVALETA YORLIN DARLIN</t>
+          <t>C001475142 - VELARDE RAMOS MELVITA YOMAR</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7294,7 +7306,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -7331,17 +7343,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>C001629991</t>
+          <t>C001504996</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>C001629991 - AVILA RODRIGUEZ LADY ROSSELLI</t>
+          <t>C001504996 - SALDAÑA NAVARRO JENY JUDITH</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H98" s="2" t="n">
@@ -7354,12 +7366,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -7369,21 +7381,9 @@
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Iniciar sesión</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7485,17 +7485,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>C004190467</t>
+          <t>C001751731</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>C004190467 - GARCIA FAJARDO JAMPOOL JUNIOR</t>
+          <t>C001751731 - RODRIGUEZ SARE JANETH ALICIA</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H100" s="2" t="n">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -7523,21 +7523,9 @@
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7547,7 +7535,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7562,12 +7550,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>C004199228</t>
+          <t>C001740965</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>C004199228 - VALDIVIESO CABRERA VICTOR MELITON</t>
+          <t>C001740965 - LAZARO NICASIO MARIBEL KARINA</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7599,7 +7587,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="O101" t="inlineStr">
         <is>
           <t>Muy dispuesto</t>
@@ -7639,17 +7631,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>C001751731</t>
+          <t>C004199228</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>C001751731 - RODRIGUEZ SARE JANETH ALICIA</t>
+          <t>C004199228 - VALDIVIESO CABRERA VICTOR MELITON</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H102" s="2" t="n">
@@ -7662,12 +7654,12 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -7677,9 +7669,21 @@
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7689,7 +7693,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7704,12 +7708,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>C001740965</t>
+          <t>C004190467</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>C001740965 - LAZARO NICASIO MARIBEL KARINA</t>
+          <t>C004190467 - GARCIA FAJARDO JAMPOOL JUNIOR</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7741,11 +7745,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
           <t>Muy dispuesto</t>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>C001513253</t>
+          <t>C001734971</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>C001513253 - RODRIGUEZ VALDIVIESO YULI DEYSI</t>
+          <t>C001734971 - ALVARADO PRADO PEDRO NILTON</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>C001734971</t>
+          <t>C001513253</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>C001734971 - ALVARADO PRADO PEDRO NILTON</t>
+          <t>C001513253 - RODRIGUEZ VALDIVIESO YULI DEYSI</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7939,17 +7939,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>C004210270</t>
+          <t>C004170162</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>C004210270 - VENEGAS VALVERDE VIOLETA IRIS</t>
+          <t>C004170162 - RODRIGUEZ RUIZ ADRIANA</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H106" s="2" t="n">
@@ -7962,12 +7962,12 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -7977,9 +7977,21 @@
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8004,17 +8016,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>C004170162</t>
+          <t>C004210270</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>C004170162 - RODRIGUEZ RUIZ ADRIANA</t>
+          <t>C004210270 - VENEGAS VALVERDE VIOLETA IRIS</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H107" s="2" t="n">
@@ -8027,12 +8039,12 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -8042,21 +8054,9 @@
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>C001732663</t>
+          <t>C001711882</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>C001732663 - ARTEAGA ACEVEDO MARIA PAULINA</t>
+          <t>C001711882 - GUEVARA CRUZ SANTOS BERNABITA</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>C001741503</t>
+          <t>C001687871</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>C001741503 - FERREL DIESTRA ALEJANDRINA TEONILA</t>
+          <t>C001687871 - ROMERO PEREZ JESSICA MEDALY</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>C001721553</t>
+          <t>C001712645</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>C001721553 - LAZARO VEGA VIRGINIA MAGDALENA</t>
+          <t>C001712645 - GUTIERREZ ROJAS ELVIN</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H116" s="2" t="n">
@@ -8684,12 +8684,12 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -8699,9 +8699,21 @@
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8726,12 +8738,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>C001401674</t>
+          <t>C001731326</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>C001401674 - DIAZ CALDERON CARMEN ROCIO</t>
+          <t>C001731326 - CAIPO SEGURA OLINDA NANCY</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8791,12 +8803,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>C001731326</t>
+          <t>C001732663</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>C001731326 - CAIPO SEGURA OLINDA NANCY</t>
+          <t>C001732663 - ARTEAGA ACEVEDO MARIA PAULINA</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8819,7 +8831,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
@@ -8856,17 +8868,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>C001711882</t>
+          <t>C001741503</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>C001711882 - GUEVARA CRUZ SANTOS BERNABITA</t>
+          <t>C001741503 - FERREL DIESTRA ALEJANDRINA TEONILA</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H119" s="2" t="n">
@@ -8879,12 +8891,12 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
@@ -8894,9 +8906,21 @@
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Iniciar sesión</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8921,17 +8945,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>C001687871</t>
+          <t>C001401674</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>C001687871 - ROMERO PEREZ JESSICA MEDALY</t>
+          <t>C001401674 - DIAZ CALDERON CARMEN ROCIO</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H120" s="2" t="n">
@@ -8944,12 +8968,12 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -8959,21 +8983,9 @@
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8998,17 +9010,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>C001712645</t>
+          <t>C001721553</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>C001712645 - GUTIERREZ ROJAS ELVIN</t>
+          <t>C001721553 - LAZARO VEGA VIRGINIA MAGDALENA</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H121" s="2" t="n">
@@ -9021,12 +9033,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -9036,21 +9048,9 @@
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>C001713673</t>
+          <t>C004173672</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>C001713673 - GUTIERREZ REYES LUPE AZUCENA</t>
+          <t>C004173672 - ROJAS JUAREZ ANA MARIA</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -9359,12 +9359,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>C001529571</t>
+          <t>C001755782</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>C001529571 - CRUZADO PULIDO LORENA LICETH</t>
+          <t>C001755782 - TORRES MATTOS ANA ROSA</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9393,25 +9393,13 @@
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No usa apps</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9436,17 +9424,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>C001737797</t>
+          <t>C001529571</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>C001737797 - RODRIGUEZ AGUSTIN LELIS ARMIDA</t>
+          <t>C001529571 - CRUZADO PULIDO LORENA LICETH</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H127" s="2" t="n">
@@ -9459,12 +9447,12 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -9474,9 +9462,21 @@
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9501,17 +9501,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>C001755782</t>
+          <t>C001737797</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>C001755782 - TORRES MATTOS ANA ROSA</t>
+          <t>C001737797 - RODRIGUEZ AGUSTIN LELIS ARMIDA</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H128" s="2" t="n">
@@ -9524,18 +9524,18 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>No usa apps</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -9551,7 +9551,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -9566,12 +9566,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>C004173672</t>
+          <t>C001713673</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>C004173672 - ROJAS JUAREZ ANA MARIA</t>
+          <t>C001713673 - GUTIERREZ REYES LUPE AZUCENA</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -9631,12 +9631,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>C001732181</t>
+          <t>C001712660</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>C001732181 - MANTILLA MINCHOLA SARA ESMENIA</t>
+          <t>C001712660 - CHAVEZ SANCHEZ MILAGROS MARIANELLA</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9665,7 +9665,7 @@
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
-          <t>No usa celular</t>
+          <t>No tiene su celular a la mano</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -9696,12 +9696,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>C001737180</t>
+          <t>C001720753</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>C001737180 - CASTILLO RAMIREZ EYLEEN JULICSA</t>
+          <t>C001720753 - CASTRO DE VENTURA JUANA</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9730,25 +9730,13 @@
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No usa celular</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q131" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9758,7 +9746,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -9773,12 +9761,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>C001733600</t>
+          <t>C001750147</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>C001733600 - REYES CABRERA MELBER AGAPITO</t>
+          <t>C001750147 - JARA GUEVARA KARINE YUDIT</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9810,11 +9798,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
         <is>
           <t>Muy dispuesto</t>
@@ -9827,7 +9811,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -9854,12 +9838,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>C001720753</t>
+          <t>C001563594</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>C001720753 - CASTRO DE VENTURA JUANA</t>
+          <t>C001563594 - GERONIMO POLO MARLENI DE JESUS</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9888,10 +9872,14 @@
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>No usa celular</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
+          <t>No usa apps</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
@@ -10046,7 +10034,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -10061,12 +10049,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>C001750147</t>
+          <t>C001737180</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>C001750147 - JARA GUEVARA KARINE YUDIT</t>
+          <t>C001737180 - CASTILLO RAMIREZ EYLEEN JULICSA</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10111,7 +10099,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -10138,12 +10126,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>C001563594</t>
+          <t>C001732181</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>C001563594 - GERONIMO POLO MARLENI DE JESUS</t>
+          <t>C001732181 - MANTILLA MINCHOLA SARA ESMENIA</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10172,14 +10160,10 @@
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr">
         <is>
-          <t>No usa apps</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>No usa celular</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
@@ -10207,12 +10191,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>C001712660</t>
+          <t>C001733600</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>C001712660 - CHAVEZ SANCHEZ MILAGROS MARIANELLA</t>
+          <t>C001733600 - REYES CABRERA MELBER AGAPITO</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10241,13 +10225,29 @@
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr">
         <is>
-          <t>No tiene su celular a la mano</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>C001564265</t>
+          <t>C001215653</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>C001564265 - ROJAS PONCE MAXIMO ESTUARDO</t>
+          <t>C001215653 - QUISPE GUEVARA SANTOS CRECENCIA</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -10682,12 +10682,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>C001215653</t>
+          <t>C001564265</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>C001215653 - QUISPE GUEVARA SANTOS CRECENCIA</t>
+          <t>C001564265 - ROJAS PONCE MAXIMO ESTUARDO</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -11575,17 +11575,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>C001558512</t>
+          <t>C001119171</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>C001558512 - GONZALES BALVERDE LUISA</t>
+          <t>C001119171 - ROMERO DE CIPRA AMELIA GOSBINDA</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H158" s="2" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L158" t="inlineStr"/>
@@ -11613,9 +11613,21 @@
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr"/>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -11640,12 +11652,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>C001577717</t>
+          <t>C001558512</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>C001577717 - MEDINA QUITO SHARON STEFANY</t>
+          <t>C001558512 - GONZALES BALVERDE LUISA</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11705,17 +11717,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>C001119171</t>
+          <t>C001577717</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>C001119171 - ROMERO DE CIPRA AMELIA GOSBINDA</t>
+          <t>C001577717 - MEDINA QUITO SHARON STEFANY</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H160" s="2" t="n">
@@ -11728,12 +11740,12 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L160" t="inlineStr"/>
@@ -11743,21 +11755,9 @@
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P160" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q160" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -13912,17 +13912,17 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>C001658298</t>
+          <t>C001179289</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>C001658298 - ABANTO DE PARIMANGO MARIA FLORA</t>
+          <t>C001179289 - ARMAS DE TOCTO MARIA CONVERCION</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H191" s="2" t="n">
@@ -13935,12 +13935,12 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L191" t="inlineStr"/>
@@ -13950,9 +13950,21 @@
         </is>
       </c>
       <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
-      <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr"/>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -13977,12 +13989,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>C004054047</t>
+          <t>C001658298</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>C004054047 - AGREDA RUIZ REBECA MILAGRITOS ESMERALDA</t>
+          <t>C001658298 - ABANTO DE PARIMANGO MARIA FLORA</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -14005,7 +14017,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L192" t="inlineStr"/>
@@ -14042,17 +14054,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>C001179289</t>
+          <t>C004054047</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>C001179289 - ARMAS DE TOCTO MARIA CONVERCION</t>
+          <t>C004054047 - AGREDA RUIZ REBECA MILAGRITOS ESMERALDA</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H193" s="2" t="n">
@@ -14065,12 +14077,12 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L193" t="inlineStr"/>
@@ -14080,21 +14092,9 @@
         </is>
       </c>
       <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P193" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q193" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -15073,17 +15073,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>C001735336</t>
+          <t>C004166670</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>C001735336 - CALDERON VILLANUEVA DORALIZ RAQUEL</t>
+          <t>C004166670 - RODRIGUEZ RODRIGUEZ GABBY ROSSI</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H208" s="2" t="n">
@@ -15096,12 +15096,12 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L208" t="inlineStr"/>
@@ -15111,9 +15111,21 @@
         </is>
       </c>
       <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr"/>
-      <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="inlineStr"/>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -15138,17 +15150,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>C004166670</t>
+          <t>C001735336</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>C004166670 - RODRIGUEZ RODRIGUEZ GABBY ROSSI</t>
+          <t>C001735336 - CALDERON VILLANUEVA DORALIZ RAQUEL</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H209" s="2" t="n">
@@ -15161,12 +15173,12 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L209" t="inlineStr"/>
@@ -15176,21 +15188,9 @@
         </is>
       </c>
       <c r="N209" t="inlineStr"/>
-      <c r="O209" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P209" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q209" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -15215,17 +15215,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>C001332646</t>
+          <t>C001125416</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>C001332646 - RODRIGUEZ ZAVALETA ROMULO ROSTANIO</t>
+          <t>C001125416 - MEDRANO OBANDO JESSICA VANESSA</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H210" s="2" t="n">
@@ -15238,18 +15238,18 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr">
         <is>
-          <t>No trabaja con alicorp, no usa apps</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N210" t="inlineStr"/>
@@ -15280,12 +15280,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>C001125416</t>
+          <t>C001415898</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>C001125416 - MEDRANO OBANDO JESSICA VANESSA</t>
+          <t>C001415898 - BALTODANO VIGO YECICA ODALIZ</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -15345,17 +15345,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>C001415898</t>
+          <t>C001332646</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>C001415898 - BALTODANO VIGO YECICA ODALIZ</t>
+          <t>C001332646 - RODRIGUEZ ZAVALETA ROMULO ROSTANIO</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H212" s="2" t="n">
@@ -15368,18 +15368,18 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No trabaja con alicorp, no usa apps</t>
         </is>
       </c>
       <c r="N212" t="inlineStr"/>
@@ -15605,12 +15605,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>C001127634</t>
+          <t>C001578039</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>C001127634 - VIDAL GARCIA TERESA</t>
+          <t>C001578039 - AGUILAR URRUTIA ROSA KELLY</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -15682,17 +15682,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>C001128962</t>
+          <t>C001667630</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>C001128962 - PAREDES HUAMAN SANTOS PETRONILA</t>
+          <t>C001667630 - RODRIGUEZ BALDERA LILIANA YOVANA</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H217" s="2" t="n">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L217" t="inlineStr"/>
@@ -15720,21 +15720,9 @@
         </is>
       </c>
       <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P217" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q217" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -15759,12 +15747,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>C001401840</t>
+          <t>C001567587</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>C001401840 - VILLARREAL CONTRERAS ANACLETO</t>
+          <t>C001567587 - RUIZ MIÑANO ROSA FLOR</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -15836,12 +15824,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>C001324442</t>
+          <t>C001401840</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>C001324442 - GUTIERREZ DE OTINIANO SANTOS NILA</t>
+          <t>C001401840 - VILLARREAL CONTRERAS ANACLETO</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -15913,12 +15901,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>C001116444</t>
+          <t>C001324442</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>C001116444 - MATTOS MENDOZA JOSE ILDELFONZO</t>
+          <t>C001324442 - GUTIERREZ DE OTINIANO SANTOS NILA</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -15947,13 +15935,25 @@
       <c r="L220" t="inlineStr"/>
       <c r="M220" t="inlineStr">
         <is>
-          <t>No usa celular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N220" t="inlineStr"/>
-      <c r="O220" t="inlineStr"/>
-      <c r="P220" t="inlineStr"/>
-      <c r="Q220" t="inlineStr"/>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -15978,12 +15978,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>C001367258</t>
+          <t>C001116444</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>C001367258 - JOAQUIN SOBERON EDITH</t>
+          <t>C001116444 - MATTOS MENDOZA JOSE ILDELFONZO</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -16012,25 +16012,13 @@
       <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No usa celular</t>
         </is>
       </c>
       <c r="N221" t="inlineStr"/>
-      <c r="O221" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P221" t="inlineStr">
-        <is>
-          <t>Iniciar sesión</t>
-        </is>
-      </c>
-      <c r="Q221" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -16055,17 +16043,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>C001667630</t>
+          <t>C001367258</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>C001667630 - RODRIGUEZ BALDERA LILIANA YOVANA</t>
+          <t>C001367258 - JOAQUIN SOBERON EDITH</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H222" s="2" t="n">
@@ -16078,12 +16066,12 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L222" t="inlineStr"/>
@@ -16093,9 +16081,21 @@
         </is>
       </c>
       <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr"/>
-      <c r="P222" t="inlineStr"/>
-      <c r="Q222" t="inlineStr"/>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Iniciar sesión</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -16120,12 +16120,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>C001567587</t>
+          <t>C001127634</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>C001567587 - RUIZ MIÑANO ROSA FLOR</t>
+          <t>C001127634 - VIDAL GARCIA TERESA</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -16197,12 +16197,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>C001578039</t>
+          <t>C001128962</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>C001578039 - AGUILAR URRUTIA ROSA KELLY</t>
+          <t>C001128962 - PAREDES HUAMAN SANTOS PETRONILA</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -16274,17 +16274,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>C004168393</t>
+          <t>C001401994</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>C004168393 - RODRIGUEZ VEGA GLORIA</t>
+          <t>C001401994 - PAREDES VDA. DE LEON MARIA ALICIA</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H225" s="2" t="n">
@@ -16297,12 +16297,12 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L225" t="inlineStr"/>
@@ -16312,21 +16312,9 @@
         </is>
       </c>
       <c r="N225" t="inlineStr"/>
-      <c r="O225" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P225" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q225" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -16481,17 +16469,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>C001401994</t>
+          <t>C004168393</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>C001401994 - PAREDES VDA. DE LEON MARIA ALICIA</t>
+          <t>C004168393 - RODRIGUEZ VEGA GLORIA</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H228" s="2" t="n">
@@ -16504,12 +16492,12 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L228" t="inlineStr"/>
@@ -16519,9 +16507,21 @@
         </is>
       </c>
       <c r="N228" t="inlineStr"/>
-      <c r="O228" t="inlineStr"/>
-      <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="inlineStr"/>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -16741,17 +16741,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>C001711123</t>
+          <t>C001488137</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>C001711123 - LAIZA ZAVALETA ESTRELLITA NELLY</t>
+          <t>C001488137 - RIOS LEON MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H232" s="2" t="n">
@@ -16764,12 +16764,12 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L232" t="inlineStr"/>
@@ -16779,21 +16779,9 @@
         </is>
       </c>
       <c r="N232" t="inlineStr"/>
-      <c r="O232" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P232" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q232" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -16818,17 +16806,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>C004241687</t>
+          <t>C004047640</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>C004241687 - MIGUEL BARRIOS ROSMERY</t>
+          <t>C004047640 - CARDENAS TIRADO MARIA PRUDENCIA</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H233" s="2" t="n">
@@ -16841,12 +16829,12 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L233" t="inlineStr"/>
@@ -16856,21 +16844,9 @@
         </is>
       </c>
       <c r="N233" t="inlineStr"/>
-      <c r="O233" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P233" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q233" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -16895,12 +16871,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>C004186187</t>
+          <t>C001711123</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>C004186187 - DIAZ SEPULVEDA SUSANA EDITH</t>
+          <t>C001711123 - LAIZA ZAVALETA ESTRELLITA NELLY</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -16929,13 +16905,25 @@
       <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr">
         <is>
-          <t>No usa apps</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N234" t="inlineStr"/>
-      <c r="O234" t="inlineStr"/>
-      <c r="P234" t="inlineStr"/>
-      <c r="Q234" t="inlineStr"/>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -16960,12 +16948,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>C004050163</t>
+          <t>C004186187</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>C004050163 - GARCIA CASTRO ROSMERY ELIZABETH</t>
+          <t>C004186187 - DIAZ SEPULVEDA SUSANA EDITH</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -16994,25 +16982,13 @@
       <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No usa apps</t>
         </is>
       </c>
       <c r="N235" t="inlineStr"/>
-      <c r="O235" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P235" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q235" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr"/>
+      <c r="Q235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -17037,17 +17013,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>C004047640</t>
+          <t>C004050163</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>C004047640 - CARDENAS TIRADO MARIA PRUDENCIA</t>
+          <t>C004050163 - GARCIA CASTRO ROSMERY ELIZABETH</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H236" s="2" t="n">
@@ -17060,12 +17036,12 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L236" t="inlineStr"/>
@@ -17075,9 +17051,21 @@
         </is>
       </c>
       <c r="N236" t="inlineStr"/>
-      <c r="O236" t="inlineStr"/>
-      <c r="P236" t="inlineStr"/>
-      <c r="Q236" t="inlineStr"/>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -17102,17 +17090,17 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>C001488137</t>
+          <t>C004241687</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>C001488137 - RIOS LEON MIGUEL ANGEL</t>
+          <t>C004241687 - MIGUEL BARRIOS ROSMERY</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H237" s="2" t="n">
@@ -17125,12 +17113,12 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L237" t="inlineStr"/>
@@ -17140,9 +17128,21 @@
         </is>
       </c>
       <c r="N237" t="inlineStr"/>
-      <c r="O237" t="inlineStr"/>
-      <c r="P237" t="inlineStr"/>
-      <c r="Q237" t="inlineStr"/>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -17167,12 +17167,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>C001676187</t>
+          <t>C004047605</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>C001676187 - GOICOCHEA AREVALO JUAN JENINFER</t>
+          <t>C004047605 - VALVERDE VARGAS DE DAGA ROSITA INES</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -17244,12 +17244,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>C001737186</t>
+          <t>C001676187</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>C001737186 - NAMAY LAVADO CASANDRA JULISSA</t>
+          <t>C001676187 - GOICOCHEA AREVALO JUAN JENINFER</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -17278,17 +17278,25 @@
       <c r="L239" t="inlineStr"/>
       <c r="M239" t="inlineStr">
         <is>
-          <t>No quiere usar app</t>
-        </is>
-      </c>
-      <c r="N239" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O239" t="inlineStr"/>
-      <c r="P239" t="inlineStr"/>
-      <c r="Q239" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -17313,12 +17321,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>C004047605</t>
+          <t>C001737186</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>C004047605 - VALVERDE VARGAS DE DAGA ROSITA INES</t>
+          <t>C001737186 - NAMAY LAVADO CASANDRA JULISSA</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -17347,25 +17355,17 @@
       <c r="L240" t="inlineStr"/>
       <c r="M240" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N240" t="inlineStr"/>
-      <c r="O240" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P240" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q240" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+          <t>No quiere usar app</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr"/>
+      <c r="P240" t="inlineStr"/>
+      <c r="Q240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -17739,12 +17739,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>C001727483</t>
+          <t>C001763751</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>C001727483 - OTINIANO FLORES DE CARBAJAL JULIA ROSA</t>
+          <t>C001763751 - GARCIA CASTRO JOSE LUIS</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -17767,7 +17767,7 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L246" t="inlineStr"/>
@@ -17804,12 +17804,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>C001763751</t>
+          <t>C001727483</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>C001763751 - GARCIA CASTRO JOSE LUIS</t>
+          <t>C001727483 - OTINIANO FLORES DE CARBAJAL JULIA ROSA</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -17832,7 +17832,7 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L247" t="inlineStr"/>
@@ -18076,12 +18076,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>C001739071</t>
+          <t>C004167851</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>C001739071 - VEREAU ROSARIO SANTOS AIDEE</t>
+          <t>C004167851 - VARAS HERNANDEZ HIMELINA ARANCEL</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18153,12 +18153,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>C004167851</t>
+          <t>C001739071</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>C004167851 - VARAS HERNANDEZ HIMELINA ARANCEL</t>
+          <t>C001739071 - VEREAU ROSARIO SANTOS AIDEE</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -18656,12 +18656,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>C001413893</t>
+          <t>C001368613</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>C001413893 - MINCHOLA VELARDE ERCILA YESENIA</t>
+          <t>C001368613 - RAMIREZ ALVA VERONICA YOVANY</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -18690,25 +18690,13 @@
       <c r="L259" t="inlineStr"/>
       <c r="M259" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Duda de la credibilidad</t>
         </is>
       </c>
       <c r="N259" t="inlineStr"/>
-      <c r="O259" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P259" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q259" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O259" t="inlineStr"/>
+      <c r="P259" t="inlineStr"/>
+      <c r="Q259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -18733,12 +18721,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>C001368613</t>
+          <t>C001413893</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>C001368613 - RAMIREZ ALVA VERONICA YOVANY</t>
+          <t>C001413893 - MINCHOLA VELARDE ERCILA YESENIA</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -18767,13 +18755,25 @@
       <c r="L260" t="inlineStr"/>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Duda de la credibilidad</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N260" t="inlineStr"/>
-      <c r="O260" t="inlineStr"/>
-      <c r="P260" t="inlineStr"/>
-      <c r="Q260" t="inlineStr"/>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -18798,12 +18798,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>C001737285</t>
+          <t>C001663917</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>C001737285 - GUTIERREZ AVILA ZULY JANETH</t>
+          <t>C001663917 - GARCIA SALAZAR MARIA JANET</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -18832,25 +18832,13 @@
       <c r="L261" t="inlineStr"/>
       <c r="M261" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No usa apps</t>
         </is>
       </c>
       <c r="N261" t="inlineStr"/>
-      <c r="O261" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P261" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q261" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O261" t="inlineStr"/>
+      <c r="P261" t="inlineStr"/>
+      <c r="Q261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -18875,12 +18863,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>C001663917</t>
+          <t>C001708611</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>C001663917 - GARCIA SALAZAR MARIA JANET</t>
+          <t>C001708611 - MINCHOLA ALVARADO PAMELA YUDITH</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -18909,7 +18897,7 @@
       <c r="L262" t="inlineStr"/>
       <c r="M262" t="inlineStr">
         <is>
-          <t>No usa apps</t>
+          <t>Celular con clave</t>
         </is>
       </c>
       <c r="N262" t="inlineStr"/>
@@ -18940,17 +18928,17 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>C001708611</t>
+          <t>C001732066</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>C001708611 - MINCHOLA ALVARADO PAMELA YUDITH</t>
+          <t>C001732066 - IPARRAGUIRRE DAVILA LORGIO JOVINO</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H263" s="2" t="n">
@@ -18963,18 +18951,18 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L263" t="inlineStr"/>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Celular con clave</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N263" t="inlineStr"/>
@@ -19005,12 +18993,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>C001732066</t>
+          <t>C001127373</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>C001732066 - IPARRAGUIRRE DAVILA LORGIO JOVINO</t>
+          <t>C001127373 - GALLARDO ORBEGOZO YANET JAQUELINE</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -19070,17 +19058,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>C001127373</t>
+          <t>C001737285</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>C001127373 - GALLARDO ORBEGOZO YANET JAQUELINE</t>
+          <t>C001737285 - GUTIERREZ AVILA ZULY JANETH</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H265" s="2" t="n">
@@ -19093,12 +19081,12 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L265" t="inlineStr"/>
@@ -19108,9 +19096,21 @@
         </is>
       </c>
       <c r="N265" t="inlineStr"/>
-      <c r="O265" t="inlineStr"/>
-      <c r="P265" t="inlineStr"/>
-      <c r="Q265" t="inlineStr"/>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -19423,17 +19423,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>C001400565</t>
+          <t>C001357277</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>C001400565 - QUISPE LOZANO SANTOS</t>
+          <t>C001357277 - ARTEAGA CRESPIN JUANITA</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H270" s="2" t="n">
@@ -19446,12 +19446,12 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L270" t="inlineStr"/>
@@ -19461,21 +19461,9 @@
         </is>
       </c>
       <c r="N270" t="inlineStr"/>
-      <c r="O270" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P270" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q270" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O270" t="inlineStr"/>
+      <c r="P270" t="inlineStr"/>
+      <c r="Q270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -19500,17 +19488,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>C001674440</t>
+          <t>C001400565</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>C001674440 - FLORES PAICO JOSE SANTOS</t>
+          <t>C001400565 - QUISPE LOZANO SANTOS</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H271" s="2" t="n">
@@ -19523,12 +19511,12 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L271" t="inlineStr"/>
@@ -19538,9 +19526,21 @@
         </is>
       </c>
       <c r="N271" t="inlineStr"/>
-      <c r="O271" t="inlineStr"/>
-      <c r="P271" t="inlineStr"/>
-      <c r="Q271" t="inlineStr"/>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -19565,12 +19565,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>C001357277</t>
+          <t>C001674440</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>C001357277 - ARTEAGA CRESPIN JUANITA</t>
+          <t>C001674440 - FLORES PAICO JOSE SANTOS</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -19760,17 +19760,17 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>C001577721</t>
+          <t>C001384058</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>C001577721 - NICASIO ACEVEDO MARTIN</t>
+          <t>C001384058 - RAMOS ROBLES YANINA BEATRIZ</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H275" s="2" t="n">
@@ -19783,12 +19783,12 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L275" t="inlineStr"/>
@@ -19798,9 +19798,21 @@
         </is>
       </c>
       <c r="N275" t="inlineStr"/>
-      <c r="O275" t="inlineStr"/>
-      <c r="P275" t="inlineStr"/>
-      <c r="Q275" t="inlineStr"/>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -19825,17 +19837,17 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>C001384058</t>
+          <t>C001577721</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>C001384058 - RAMOS ROBLES YANINA BEATRIZ</t>
+          <t>C001577721 - NICASIO ACEVEDO MARTIN</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H276" s="2" t="n">
@@ -19848,12 +19860,12 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L276" t="inlineStr"/>
@@ -19863,21 +19875,9 @@
         </is>
       </c>
       <c r="N276" t="inlineStr"/>
-      <c r="O276" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P276" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q276" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="O276" t="inlineStr"/>
+      <c r="P276" t="inlineStr"/>
+      <c r="Q276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -20677,12 +20677,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>C001577408</t>
+          <t>C001740647</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>C001577408 - CABRERA LOYOLA DIANA MILY</t>
+          <t>C001740647 - SILVA DOMINGUEZ MIRIAM</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -20754,12 +20754,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>C001740647</t>
+          <t>C001577408</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>C001740647 - SILVA DOMINGUEZ MIRIAM</t>
+          <t>C001577408 - CABRERA LOYOLA DIANA MILY</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -21245,17 +21245,17 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>C001504436</t>
+          <t>C001528680</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>C001504436 - SIFUENTES ALTAMIRANO EDY JOEL</t>
+          <t>C001528680 - RUBIO PAREDES SANTOS KARINA</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H296" s="2" t="n">
@@ -21268,25 +21268,21 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L296" t="inlineStr"/>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Tiene iphone</t>
-        </is>
-      </c>
-      <c r="N296" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr"/>
       <c r="O296" t="inlineStr"/>
       <c r="P296" t="inlineStr"/>
       <c r="Q296" t="inlineStr"/>
@@ -21314,12 +21310,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>C001522090</t>
+          <t>C001274741</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>C001522090 - HENRIQUEZ CARRANZA GENOVEVA ROSIS</t>
+          <t>C001274741 - ACUNA VALVERDE TERESA FRANCISCA</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -21342,7 +21338,7 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L297" t="inlineStr"/>
@@ -21379,17 +21375,17 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>C001274741</t>
+          <t>C001504436</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>C001274741 - ACUNA VALVERDE TERESA FRANCISCA</t>
+          <t>C001504436 - SIFUENTES ALTAMIRANO EDY JOEL</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H298" s="2" t="n">
@@ -21402,21 +21398,25 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L298" t="inlineStr"/>
       <c r="M298" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N298" t="inlineStr"/>
+          <t>Tiene iphone</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="inlineStr"/>
       <c r="Q298" t="inlineStr"/>
@@ -21444,12 +21444,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>C001528680</t>
+          <t>C001522090</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>C001528680 - RUBIO PAREDES SANTOS KARINA</t>
+          <t>C001522090 - HENRIQUEZ CARRANZA GENOVEVA ROSIS</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -21716,17 +21716,17 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>C001525984</t>
+          <t>C001274746</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>C001525984 - LAIZA CASTILLO SABINA</t>
+          <t>C001274746 - LAVADO VALDERRAMA SARA BENILDA</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H303" s="2" t="n">
@@ -21739,25 +21739,21 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L303" t="inlineStr"/>
       <c r="M303" t="inlineStr">
         <is>
-          <t>No usa smartphone</t>
-        </is>
-      </c>
-      <c r="N303" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr"/>
       <c r="O303" t="inlineStr"/>
       <c r="P303" t="inlineStr"/>
       <c r="Q303" t="inlineStr"/>
@@ -21785,17 +21781,17 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>C001274746</t>
+          <t>C001525984</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>C001274746 - LAVADO VALDERRAMA SARA BENILDA</t>
+          <t>C001525984 - LAIZA CASTILLO SABINA</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H304" s="2" t="n">
@@ -21808,21 +21804,25 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L304" t="inlineStr"/>
       <c r="M304" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N304" t="inlineStr"/>
+          <t>No usa smartphone</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="O304" t="inlineStr"/>
       <c r="P304" t="inlineStr"/>
       <c r="Q304" t="inlineStr"/>
@@ -21915,17 +21915,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>C001284684</t>
+          <t>C001285463</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>C001284684 - OLOYA LAIZA OLGA MARIBEL</t>
+          <t>C001285463 - DE LA CRUZ ROMAN CLARA</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H306" s="2" t="n">
@@ -21938,12 +21938,12 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L306" t="inlineStr"/>
@@ -21953,9 +21953,21 @@
         </is>
       </c>
       <c r="N306" t="inlineStr"/>
-      <c r="O306" t="inlineStr"/>
-      <c r="P306" t="inlineStr"/>
-      <c r="Q306" t="inlineStr"/>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -21980,17 +21992,17 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>C001284814</t>
+          <t>C001521872</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>C001284814 - RAMIREZ VERA LUZ CELMIRA</t>
+          <t>C001521872 - GRAOS BRICENO FREDY RONALD</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H307" s="2" t="n">
@@ -22003,12 +22015,12 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L307" t="inlineStr"/>
@@ -22018,14 +22030,26 @@
         </is>
       </c>
       <c r="N307" t="inlineStr"/>
-      <c r="O307" t="inlineStr"/>
-      <c r="P307" t="inlineStr"/>
-      <c r="Q307" t="inlineStr"/>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>HUAMACHUCO</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -22045,12 +22069,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>C001455878</t>
+          <t>C001307309</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>C001455878 - JULCA NEYRA LUIS JAIME</t>
+          <t>C001307309 - MORALES RAMIREZ JUAN FERNANDO</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -22079,25 +22103,17 @@
       <c r="L308" t="inlineStr"/>
       <c r="M308" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N308" t="inlineStr"/>
-      <c r="O308" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P308" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q308" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+          <t>No abre el app en su celular</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr"/>
+      <c r="P308" t="inlineStr"/>
+      <c r="Q308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -22122,17 +22138,17 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>C001285463</t>
+          <t>C001284684</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>C001285463 - DE LA CRUZ ROMAN CLARA</t>
+          <t>C001284684 - OLOYA LAIZA OLGA MARIBEL</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H309" s="2" t="n">
@@ -22145,12 +22161,12 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L309" t="inlineStr"/>
@@ -22160,21 +22176,9 @@
         </is>
       </c>
       <c r="N309" t="inlineStr"/>
-      <c r="O309" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P309" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q309" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O309" t="inlineStr"/>
+      <c r="P309" t="inlineStr"/>
+      <c r="Q309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -22199,17 +22203,17 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>C001521872</t>
+          <t>C001284814</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>C001521872 - GRAOS BRICENO FREDY RONALD</t>
+          <t>C001284814 - RAMIREZ VERA LUZ CELMIRA</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H310" s="2" t="n">
@@ -22222,12 +22226,12 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L310" t="inlineStr"/>
@@ -22237,26 +22241,14 @@
         </is>
       </c>
       <c r="N310" t="inlineStr"/>
-      <c r="O310" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P310" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q310" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O310" t="inlineStr"/>
+      <c r="P310" t="inlineStr"/>
+      <c r="Q310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>HUAMACHUCO</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -22276,12 +22268,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>C001307309</t>
+          <t>C001455878</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>C001307309 - MORALES RAMIREZ JUAN FERNANDO</t>
+          <t>C001455878 - JULCA NEYRA LUIS JAIME</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -22310,17 +22302,25 @@
       <c r="L311" t="inlineStr"/>
       <c r="M311" t="inlineStr">
         <is>
-          <t>No abre el app en su celular</t>
-        </is>
-      </c>
-      <c r="N311" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O311" t="inlineStr"/>
-      <c r="P311" t="inlineStr"/>
-      <c r="Q311" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr"/>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -24066,12 +24066,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>C001521896</t>
+          <t>C001408605</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>C001521896 - VASQUEZ ACOSTA MARIA ROXANI</t>
+          <t>C001408605 - SANDOVAL ARANDA ELCIRA</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -24100,25 +24100,13 @@
       <c r="L337" t="inlineStr"/>
       <c r="M337" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No usa apps</t>
         </is>
       </c>
       <c r="N337" t="inlineStr"/>
-      <c r="O337" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P337" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q337" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O337" t="inlineStr"/>
+      <c r="P337" t="inlineStr"/>
+      <c r="Q337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -24143,12 +24131,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>C001444741</t>
+          <t>C001521896</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>C001444741 - MUNOZ DE PAREDES LUCIA</t>
+          <t>C001521896 - VASQUEZ ACOSTA MARIA ROXANI</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -24220,12 +24208,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>C001448981</t>
+          <t>C001444741</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>C001448981 - SANDOVAL CRUZ DE GRADOS DAMIANA</t>
+          <t>C001444741 - MUNOZ DE PAREDES LUCIA</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -24297,12 +24285,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>C001408605</t>
+          <t>C001448981</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>C001408605 - SANDOVAL ARANDA ELCIRA</t>
+          <t>C001448981 - SANDOVAL CRUZ DE GRADOS DAMIANA</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -24331,13 +24319,25 @@
       <c r="L340" t="inlineStr"/>
       <c r="M340" t="inlineStr">
         <is>
-          <t>No usa apps</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N340" t="inlineStr"/>
-      <c r="O340" t="inlineStr"/>
-      <c r="P340" t="inlineStr"/>
-      <c r="Q340" t="inlineStr"/>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -24492,12 +24492,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>C004244367</t>
+          <t>C004241784</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>C004244367 - TORIBIO HONORIO LIZ VERONICA</t>
+          <t>C004241784 - RAMOS VALENCIA CONSUELO HAYDEE</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -24526,13 +24526,25 @@
       <c r="L343" t="inlineStr"/>
       <c r="M343" t="inlineStr">
         <is>
-          <t>No hay promociones, prefere comprar en el mayorista</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N343" t="inlineStr"/>
-      <c r="O343" t="inlineStr"/>
-      <c r="P343" t="inlineStr"/>
-      <c r="Q343" t="inlineStr"/>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -24634,12 +24646,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>C004241784</t>
+          <t>C004244367</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>C004241784 - RAMOS VALENCIA CONSUELO HAYDEE</t>
+          <t>C004244367 - TORIBIO HONORIO LIZ VERONICA</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -24668,25 +24680,13 @@
       <c r="L345" t="inlineStr"/>
       <c r="M345" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No hay promociones, prefere comprar en el mayorista</t>
         </is>
       </c>
       <c r="N345" t="inlineStr"/>
-      <c r="O345" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P345" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q345" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O345" t="inlineStr"/>
+      <c r="P345" t="inlineStr"/>
+      <c r="Q345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -24711,12 +24711,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>C001763375</t>
+          <t>C004060767</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>C001763375 - ROJAS YUPANQUI GABY ZULEMA</t>
+          <t>C004060767 - VEGA ARGOMEDO LUIS ALBERTO</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -24745,13 +24745,25 @@
       <c r="L346" t="inlineStr"/>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Ya no hace pedidos, va cambiar de codigo</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N346" t="inlineStr"/>
-      <c r="O346" t="inlineStr"/>
-      <c r="P346" t="inlineStr"/>
-      <c r="Q346" t="inlineStr"/>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -24776,12 +24788,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>C004060767</t>
+          <t>C001763375</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>C004060767 - VEGA ARGOMEDO LUIS ALBERTO</t>
+          <t>C001763375 - ROJAS YUPANQUI GABY ZULEMA</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -24810,25 +24822,13 @@
       <c r="L347" t="inlineStr"/>
       <c r="M347" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ya no hace pedidos, va cambiar de codigo</t>
         </is>
       </c>
       <c r="N347" t="inlineStr"/>
-      <c r="O347" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P347" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q347" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O347" t="inlineStr"/>
+      <c r="P347" t="inlineStr"/>
+      <c r="Q347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -25267,12 +25267,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>C001641758</t>
+          <t>C001128320</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>C001641758 - QUISPE ARMAS CARLOS HUMBERTO</t>
+          <t>C001128320 - RODRIGUEZ GARCIA YANIRA EDITH</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
@@ -25304,14 +25304,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N354" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O354" t="inlineStr"/>
-      <c r="P354" t="inlineStr"/>
-      <c r="Q354" t="inlineStr"/>
+      <c r="N354" t="inlineStr"/>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -25336,12 +25344,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>C001674629</t>
+          <t>C001762232</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>C001674629 - VASQUEZ MENDEZ HILDA PALMIRA</t>
+          <t>C001762232 - TUESTAS ABANTO MARIA ESTHER</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
@@ -25370,25 +25378,13 @@
       <c r="L355" t="inlineStr"/>
       <c r="M355" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No usa apps</t>
         </is>
       </c>
       <c r="N355" t="inlineStr"/>
-      <c r="O355" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P355" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q355" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O355" t="inlineStr"/>
+      <c r="P355" t="inlineStr"/>
+      <c r="Q355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -25413,12 +25409,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>C001734919</t>
+          <t>C004054236</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>C001734919 - FIGUEROA RAZA ELIZABETH</t>
+          <t>C004054236 - AGUILAR VASQUEZ ARMANDO</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
@@ -25478,17 +25474,17 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>C001731621</t>
+          <t>C001641758</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>C001731621 - AGREDA ALZA LIDIA ANABELLA</t>
+          <t>C001641758 - QUISPE ARMAS CARLOS HUMBERTO</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H357" s="2" t="n">
@@ -25501,12 +25497,12 @@
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L357" t="inlineStr"/>
@@ -25515,7 +25511,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N357" t="inlineStr"/>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="O357" t="inlineStr"/>
       <c r="P357" t="inlineStr"/>
       <c r="Q357" t="inlineStr"/>
@@ -25543,12 +25543,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>C001762232</t>
+          <t>C001674629</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>C001762232 - TUESTAS ABANTO MARIA ESTHER</t>
+          <t>C001674629 - VASQUEZ MENDEZ HILDA PALMIRA</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
@@ -25577,13 +25577,25 @@
       <c r="L358" t="inlineStr"/>
       <c r="M358" t="inlineStr">
         <is>
-          <t>No usa apps</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N358" t="inlineStr"/>
-      <c r="O358" t="inlineStr"/>
-      <c r="P358" t="inlineStr"/>
-      <c r="Q358" t="inlineStr"/>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -25608,12 +25620,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>C004054236</t>
+          <t>C001731621</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>C004054236 - AGUILAR VASQUEZ ARMANDO</t>
+          <t>C001731621 - AGREDA ALZA LIDIA ANABELLA</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -25673,17 +25685,17 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>C001128320</t>
+          <t>C001734919</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>C001128320 - RODRIGUEZ GARCIA YANIRA EDITH</t>
+          <t>C001734919 - FIGUEROA RAZA ELIZABETH</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H360" s="2" t="n">
@@ -25696,12 +25708,12 @@
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L360" t="inlineStr"/>
@@ -25711,21 +25723,9 @@
         </is>
       </c>
       <c r="N360" t="inlineStr"/>
-      <c r="O360" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P360" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q360" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O360" t="inlineStr"/>
+      <c r="P360" t="inlineStr"/>
+      <c r="Q360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -25827,17 +25827,17 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>C004192601</t>
+          <t>C004190848</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>C004192601 - CARLOS RODRIGUEZ MARLENI LUZVENI</t>
+          <t>C004190848 - VIDAL PONCE MATILDE TEONILA</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H362" s="2" t="n">
@@ -25850,12 +25850,12 @@
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L362" t="inlineStr"/>
@@ -25865,21 +25865,9 @@
         </is>
       </c>
       <c r="N362" t="inlineStr"/>
-      <c r="O362" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P362" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q362" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="O362" t="inlineStr"/>
+      <c r="P362" t="inlineStr"/>
+      <c r="Q362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -25904,17 +25892,17 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>C004175425</t>
+          <t>C004192601</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>C004175425 - GERMAN MENDIETA ANA MARIA</t>
+          <t>C004192601 - CARLOS RODRIGUEZ MARLENI LUZVENI</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H363" s="2" t="n">
@@ -25927,12 +25915,12 @@
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L363" t="inlineStr"/>
@@ -25942,9 +25930,21 @@
         </is>
       </c>
       <c r="N363" t="inlineStr"/>
-      <c r="O363" t="inlineStr"/>
-      <c r="P363" t="inlineStr"/>
-      <c r="Q363" t="inlineStr"/>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -25969,17 +25969,17 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>C004190848</t>
+          <t>C001706144</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>C004190848 - VIDAL PONCE MATILDE TEONILA</t>
+          <t>C001706144 - BARRIOS AGUIRRE NATALI AIME</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H364" s="2" t="n">
@@ -25992,12 +25992,12 @@
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L364" t="inlineStr"/>
@@ -26007,9 +26007,21 @@
         </is>
       </c>
       <c r="N364" t="inlineStr"/>
-      <c r="O364" t="inlineStr"/>
-      <c r="P364" t="inlineStr"/>
-      <c r="Q364" t="inlineStr"/>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -26034,17 +26046,17 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>C001706144</t>
+          <t>C001617486</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>C001706144 - BARRIOS AGUIRRE NATALI AIME</t>
+          <t>C001617486 - MORALES MENDEZ HILDER LEONARDO</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H365" s="2" t="n">
@@ -26057,12 +26069,12 @@
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado Definitivamente</t>
         </is>
       </c>
       <c r="L365" t="inlineStr"/>
@@ -26072,21 +26084,9 @@
         </is>
       </c>
       <c r="N365" t="inlineStr"/>
-      <c r="O365" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P365" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q365" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O365" t="inlineStr"/>
+      <c r="P365" t="inlineStr"/>
+      <c r="Q365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -26330,17 +26330,17 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>C001617486</t>
+          <t>C001767433</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>C001617486 - MORALES MENDEZ HILDER LEONARDO</t>
+          <t>C001767433 - RODRIGUEZ BEJARANO SEGUNDO EUSEBIO</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H369" s="2" t="n">
@@ -26353,12 +26353,12 @@
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>PDV Cerrado Definitivamente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L369" t="inlineStr"/>
@@ -26368,9 +26368,21 @@
         </is>
       </c>
       <c r="N369" t="inlineStr"/>
-      <c r="O369" t="inlineStr"/>
-      <c r="P369" t="inlineStr"/>
-      <c r="Q369" t="inlineStr"/>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -26395,17 +26407,17 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>C001767433</t>
+          <t>C004167425</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>C001767433 - RODRIGUEZ BEJARANO SEGUNDO EUSEBIO</t>
+          <t>C004167425 - FELIPE BAZAN DE ROJAS BETTY MARUJA</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H370" s="2" t="n">
@@ -26418,12 +26430,12 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L370" t="inlineStr"/>
@@ -26433,21 +26445,9 @@
         </is>
       </c>
       <c r="N370" t="inlineStr"/>
-      <c r="O370" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P370" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q370" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O370" t="inlineStr"/>
+      <c r="P370" t="inlineStr"/>
+      <c r="Q370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -26472,12 +26472,12 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>C004167425</t>
+          <t>C004175425</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>C004167425 - FELIPE BAZAN DE ROJAS BETTY MARUJA</t>
+          <t>C004175425 - GERMAN MENDIETA ANA MARIA</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -26537,12 +26537,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>C001216214</t>
+          <t>C001326631</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>C001216214 - MALDONADO TRUJILLO DE VILLARREAL ASUNCIO</t>
+          <t>C001326631 - ESQUIVEL DE SANCHEZ JUANA</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -26571,25 +26571,13 @@
       <c r="L372" t="inlineStr"/>
       <c r="M372" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No usa celular</t>
         </is>
       </c>
       <c r="N372" t="inlineStr"/>
-      <c r="O372" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P372" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="Q372" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O372" t="inlineStr"/>
+      <c r="P372" t="inlineStr"/>
+      <c r="Q372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -26614,12 +26602,12 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>C001122173</t>
+          <t>C001345662</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>C001122173 - ESTEBAN POLO MARIA</t>
+          <t>C001345662 - MAURICIO DE LA CRUZ EUGENIA</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -26691,17 +26679,17 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>C001122249</t>
+          <t>C001122173</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>C001122249 - SALINAS CRUZ DE FLOREANO ELCIRA AZUCENA</t>
+          <t>C001122173 - ESTEBAN POLO MARIA</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H374" s="2" t="n">
@@ -26714,12 +26702,12 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L374" t="inlineStr"/>
@@ -26729,9 +26717,21 @@
         </is>
       </c>
       <c r="N374" t="inlineStr"/>
-      <c r="O374" t="inlineStr"/>
-      <c r="P374" t="inlineStr"/>
-      <c r="Q374" t="inlineStr"/>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -26756,17 +26756,17 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>C001326631</t>
+          <t>C001122249</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>C001326631 - ESQUIVEL DE SANCHEZ JUANA</t>
+          <t>C001122249 - SALINAS CRUZ DE FLOREANO ELCIRA AZUCENA</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H375" s="2" t="n">
@@ -26779,18 +26779,18 @@
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L375" t="inlineStr"/>
       <c r="M375" t="inlineStr">
         <is>
-          <t>No usa celular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N375" t="inlineStr"/>
@@ -26821,12 +26821,12 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>C001345662</t>
+          <t>C001216214</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>C001345662 - MAURICIO DE LA CRUZ EUGENIA</t>
+          <t>C001216214 - MALDONADO TRUJILLO DE VILLARREAL ASUNCIO</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
